--- a/src/attributions/attributions_ig_traj_412.xlsx
+++ b/src/attributions/attributions_ig_traj_412.xlsx
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04359552118848911</v>
+        <v>0.02048738991857044</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1011,25 +1011,25 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001756677835986827</v>
+        <v>-0.005394123620966996</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-6.380483803514161e-11</v>
+        <v>-1.497325763763896e-11</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0943772008801398</v>
+        <v>0.1015857385853489</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1038,25 +1038,25 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.01706288549209529</v>
+        <v>-0.04350285541698768</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.1108393493920033</v>
+        <v>-0.01760546760263797</v>
       </c>
       <c r="S2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0780399969330271</v>
+        <v>0.01611293117539966</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
@@ -1065,52 +1065,52 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.03579794656891998</v>
+        <v>-0.03884301698448741</v>
       </c>
       <c r="X2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.04193801210966939</v>
+        <v>0.001716985018901608</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.03574435295838943</v>
+        <v>-0.02241392568823886</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.03990838014970763</v>
+        <v>-0.03088873464390079</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.03011334343262151</v>
+        <v>0.01578024470755522</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.06984995705226744</v>
+        <v>0.0286752552202828</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -1119,25 +1119,25 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.06764043476254365</v>
+        <v>-0.003475797862123345</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.03825845425710213</v>
+        <v>0.004070614654535456</v>
       </c>
       <c r="AT2" t="n">
         <v>-0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.3688543517873764</v>
+        <v>0.1786172121027065</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.2143844191366335</v>
+        <v>-0.03695508827982726</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -1155,16 +1155,16 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0.05067770850510866</v>
+        <v>-0.002163010595139302</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.0124367508303029</v>
+        <v>-0.003938219314915014</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -1173,61 +1173,61 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.006884330678400366</v>
+        <v>-0.004488980961305782</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0.02993555951146837</v>
+        <v>-0.00698211810484515</v>
       </c>
       <c r="BL2" t="n">
         <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.01794557301531623</v>
+        <v>0.007719230438059603</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
         <v>-0</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.1125886254884709</v>
+        <v>0.03503085306610976</v>
       </c>
       <c r="BQ2" t="n">
         <v>-0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.03836415641111152</v>
+        <v>0.0105517600578041</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.2190435714290547</v>
+        <v>0.08124296859349199</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX2" t="n">
         <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.01959831959694342</v>
+        <v>-0.0298604641326557</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1236,151 +1236,151 @@
         <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.08553952934754498</v>
+        <v>-0.01647305894827327</v>
       </c>
       <c r="CD2" t="n">
         <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.05375344145653691</v>
+        <v>-0.0432827686379576</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
         <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.005478452444445255</v>
+        <v>0.01935269990703759</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.07485097501229115</v>
+        <v>0.01647398785571319</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.01197765096993872</v>
+        <v>-0.03871614505496043</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.08543697416382008</v>
+        <v>0.01153664557302507</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
         <v>-0</v>
       </c>
       <c r="CT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.005521092723554493</v>
+        <v>0.01009747244994217</v>
       </c>
       <c r="CV2" t="n">
         <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.05532201692700216</v>
+        <v>-0.04404598343218877</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.0140529844267339</v>
+        <v>0.01398944994378917</v>
       </c>
       <c r="DA2" t="n">
         <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.05877146954848517</v>
+        <v>0.01889424138216796</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.09700170749580087</v>
+        <v>-0.07273068378103355</v>
       </c>
       <c r="DG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH2" t="n">
         <v>0</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.05825522326555194</v>
+        <v>-0.01114819461168467</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.02681955538285876</v>
+        <v>0.01133691036447205</v>
       </c>
       <c r="DN2" t="n">
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.01640801157107596</v>
+        <v>-0.01985614717195235</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.04093867970434654</v>
+        <v>0.03202792645347331</v>
       </c>
       <c r="DS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0.024682281284329</v>
+        <v>0.02323886083698573</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.2305556636655283</v>
+        <v>-0.04620202959406314</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
@@ -1389,10 +1389,10 @@
         <v>-0</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.002082477280989771</v>
+        <v>-0.01572858438353978</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
@@ -1401,22 +1401,22 @@
         <v>-0</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0.04318179717736433</v>
+        <v>-0.004591197796931427</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.00549125236658555</v>
+        <v>-0.03026444856618377</v>
       </c>
       <c r="EH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI2" t="n">
         <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.05007524833202313</v>
+        <v>-0.005547981276858452</v>
       </c>
       <c r="EK2" t="n">
         <v>-0</v>
@@ -1425,70 +1425,70 @@
         <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.1103624871458796</v>
+        <v>0.01429499506974298</v>
       </c>
       <c r="EO2" t="n">
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.02232203605040389</v>
+        <v>-0.002204846717284035</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.03886949220018341</v>
+        <v>0.01399477091395488</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.09586515540903622</v>
+        <v>0.02332020089452148</v>
       </c>
       <c r="EX2" t="n">
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.06835285609203957</v>
+        <v>-0.05540264238332564</v>
       </c>
       <c r="EZ2" t="n">
         <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.00251997554343901</v>
+        <v>0.0104206360916638</v>
       </c>
       <c r="FC2" t="n">
         <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.05493762940755003</v>
+        <v>0.01640976580450234</v>
       </c>
       <c r="FG2" t="n">
         <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.05413503492444798</v>
+        <v>0.03838869015949937</v>
       </c>
       <c r="FI2" t="n">
         <v>-0</v>
@@ -1497,7 +1497,7 @@
         <v>-0</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.1116893326413389</v>
+        <v>-0.006115004765825808</v>
       </c>
       <c r="FL2" t="n">
         <v>-0</v>
@@ -1509,40 +1509,40 @@
         <v>0</v>
       </c>
       <c r="FO2" t="n">
-        <v>-0.005895062890938918</v>
+        <v>0.03754380271839868</v>
       </c>
       <c r="FP2" t="n">
         <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.004549341830389582</v>
+        <v>-0.01122460809284081</v>
       </c>
       <c r="FR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS2" t="n">
         <v>-0</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.006665039483991953</v>
+        <v>0.009635750646894521</v>
       </c>
       <c r="FU2" t="n">
         <v>-0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0.0345229180109282</v>
+        <v>-0.004410413333356682</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.05118904873769858</v>
+        <v>-0.03264997825498916</v>
       </c>
       <c r="GA2" t="n">
         <v>0</v>
@@ -1551,19 +1551,19 @@
         <v>-0</v>
       </c>
       <c r="GC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF2" t="n">
         <v>-0</v>
       </c>
       <c r="GG2" t="n">
-        <v>-0.04974938493857682</v>
+        <v>-0.01426403277786163</v>
       </c>
     </row>
     <row r="3">
@@ -2706,10 +2706,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1332520309645787</v>
+        <v>0.001282563412627352</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2718,16 +2718,16 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.02247548209885781</v>
+        <v>-6.808928733940324e-05</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.02827394583314968</v>
+        <v>-7.639020971556958e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2260710736976217</v>
+        <v>0.004365711473399932</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2745,79 +2745,79 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.04265428207532999</v>
+        <v>-0.0002563435746172424</v>
       </c>
       <c r="O5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.08623940722537077</v>
+        <v>-0.001313361296456058</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5" t="n">
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1746420024267494</v>
+        <v>8.599057948727766e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.165700875493322</v>
+        <v>-0.002388638027883904</v>
       </c>
       <c r="X5" t="n">
         <v>-0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.01877203507736671</v>
+        <v>-0.0001757130564737927</v>
       </c>
       <c r="Z5" t="n">
         <v>-0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1018126498534377</v>
+        <v>-0.0007247699413599608</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.04471378738092713</v>
+        <v>-0.001224628601883394</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.005683363733538275</v>
+        <v>-0.0008184771207742814</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.07093869491061898</v>
+        <v>0.0005855550599318529</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
@@ -2826,16 +2826,16 @@
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.03284130131397773</v>
+        <v>0.0005245429154952636</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.0402387879068019</v>
+        <v>-0.0001647281166918501</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
@@ -2844,34 +2844,34 @@
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3489098983716646</v>
+        <v>0.007775146432448111</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.207724796134623</v>
+        <v>-0.0005387595413975739</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.2070170477828917</v>
+        <v>-0.0002137242175197971</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.00238359310422465</v>
+        <v>-0.0002447362073011378</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,13 +2880,13 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.02968076478963176</v>
+        <v>-0.000295731710515416</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.002702745589581721</v>
+        <v>6.901171382762873e-05</v>
       </c>
       <c r="BJ5" t="n">
         <v>-0</v>
@@ -2895,10 +2895,10 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.05230340458120407</v>
+        <v>0.001629340504752069</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
@@ -2907,13 +2907,13 @@
         <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.06917546714237122</v>
+        <v>0.001923940851257955</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.04407538008632336</v>
+        <v>-0.0009110439901371037</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,52 +2925,52 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1748329460637267</v>
+        <v>0.00379499069716725</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.1601212400342848</v>
+        <v>-0.0003768308202532352</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.09418881510832644</v>
+        <v>3.659282011841121e-05</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.1190006882109157</v>
+        <v>-0.0008722046913202363</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.02736520148705055</v>
+        <v>-0.0003219349601953247</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.04095676521668259</v>
+        <v>0.0002997058439233125</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
         <v>-0</v>
@@ -2979,22 +2979,22 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.006353406479585512</v>
+        <v>-0.00267821767621808</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.1212181423344907</v>
+        <v>-0.0002700268903836061</v>
       </c>
       <c r="CR5" t="n">
         <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.006818620899054596</v>
+        <v>-8.34789686417193e-05</v>
       </c>
       <c r="CT5" t="n">
         <v>0</v>
@@ -3003,25 +3003,25 @@
         <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.1175466102871642</v>
+        <v>-0.0009931999596035238</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.001390049843010575</v>
+        <v>-0.000522221763611888</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.059531898217187</v>
+        <v>0.000604533928482383</v>
       </c>
       <c r="DC5" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.1068730037175078</v>
+        <v>-0.002642835985755877</v>
       </c>
       <c r="DG5" t="n">
         <v>-0</v>
@@ -3042,13 +3042,13 @@
         <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.07345193700609701</v>
+        <v>-0.002278586701820533</v>
       </c>
       <c r="DJ5" t="n">
         <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.02520612217804258</v>
+        <v>0.0003348396274653047</v>
       </c>
       <c r="DL5" t="n">
         <v>-0</v>
@@ -3057,52 +3057,52 @@
         <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.05810835659694037</v>
+        <v>-0.001190222862161804</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.04022723189490172</v>
+        <v>9.949287785627105e-05</v>
       </c>
       <c r="DS5" t="n">
         <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.002904793487715817</v>
+        <v>0.002109402973756665</v>
       </c>
       <c r="DU5" t="n">
         <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.1761069832414308</v>
+        <v>0.0002425998785383563</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.07515272725821179</v>
+        <v>-0.002369496441707143</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.03049224434279381</v>
+        <v>0.001972710529072788</v>
       </c>
       <c r="ED5" t="n">
         <v>-0</v>
@@ -3114,7 +3114,7 @@
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.04325536048515159</v>
+        <v>-0.001326349527784499</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
@@ -3123,16 +3123,16 @@
         <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.018287146505006</v>
+        <v>-0.0006433499379128668</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.06211587892497267</v>
+        <v>-0.0003151413583948117</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
@@ -3141,22 +3141,22 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.05131365834849041</v>
+        <v>0.0002744325115386433</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
         <v>-0</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.0439829314769385</v>
+        <v>0.0001683836978560339</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.03529447601800668</v>
+        <v>0.001906551976669568</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3165,25 +3165,25 @@
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.1202917358999288</v>
+        <v>-0.001684173760645327</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.01827731021371319</v>
+        <v>-0.0009066997756248556</v>
       </c>
       <c r="FC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.05795073046286316</v>
+        <v>0.0005602837139082979</v>
       </c>
       <c r="FE5" t="n">
         <v>-0</v>
@@ -3192,82 +3192,82 @@
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.01740730972531061</v>
+        <v>0.001564705348124747</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.1137170070868718</v>
+        <v>-0.0008704145191310387</v>
       </c>
       <c r="FL5" t="n">
         <v>0</v>
       </c>
       <c r="FM5" t="n">
-        <v>-0.001254630612687913</v>
+        <v>-0.0004206116504049023</v>
       </c>
       <c r="FN5" t="n">
         <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.01711202593581722</v>
+        <v>1.567226590329089e-05</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.006512258913313799</v>
+        <v>0.0002286363619113432</v>
       </c>
       <c r="FU5" t="n">
         <v>-0</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.06977655799078838</v>
+        <v>0.0002576913982379487</v>
       </c>
       <c r="FW5" t="n">
         <v>-0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.06670085099684286</v>
+        <v>-0.0006816748131905599</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
         <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
-        <v>-0.01711551771205607</v>
+        <v>0.001334692434618374</v>
       </c>
       <c r="GF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG5" t="n">
         <v>-0</v>
@@ -3847,25 +3847,25 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2519893726468023</v>
+        <v>0.22538609120594</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1734993420737204</v>
+        <v>-0.1633765905248946</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0214772419718932</v>
+        <v>-0.003962360160368618</v>
       </c>
       <c r="F7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3874,22 +3874,22 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.319139588588151</v>
+        <v>0.4078972844930199</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2263650882916788</v>
+        <v>-0.2216954665291746</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.03229737401075999</v>
+        <v>-0.07067241523893217</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -3898,25 +3898,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.198294969442334</v>
+        <v>0.2029955105517183</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.006233792620008598</v>
+        <v>-0.05207390833799574</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1754056990284446</v>
+        <v>-0.03696535042338514</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -3925,55 +3925,55 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.07990405661517595</v>
+        <v>-0.03894580785058345</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.001215425907683058</v>
+        <v>-0.05148849543330922</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.0184915208824566</v>
+        <v>-0.05236483815889365</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.02951921648324635</v>
+        <v>0.205265718894437</v>
       </c>
       <c r="AM7" t="n">
         <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.1573684806121315</v>
+        <v>-0.1081201786460848</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.06796308751432056</v>
+        <v>0.1431850852410178</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ7" t="n">
         <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
         <v>-0</v>
@@ -3982,43 +3982,43 @@
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.5099506490712726</v>
+        <v>0.5036979599641068</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.06436499425115164</v>
+        <v>-0.2316490996356241</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.3151226515453426</v>
+        <v>-0.1740200660718083</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.006301467805114655</v>
+        <v>-0.01620412374114766</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.03423590174378047</v>
+        <v>-0.04266060042412807</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.02766312366552436</v>
+        <v>-0.01449794257116086</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4036,22 +4036,22 @@
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.01023555114760323</v>
+        <v>-0.009148918497774799</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0377171483444882</v>
+        <v>0.03842864569170102</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1326742849498833</v>
+        <v>0.02206357146960825</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
@@ -4063,49 +4063,49 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.2412988912674505</v>
+        <v>0.4607718872685066</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.02184508619350496</v>
+        <v>-0.1329749101984471</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.1744174107250956</v>
+        <v>-0.02483394419634429</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.1393767796115133</v>
+        <v>-0.1753567473568989</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.03809336786254391</v>
+        <v>0.1644489108913585</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.02773683632202575</v>
+        <v>-0.04306529566277458</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
@@ -4117,19 +4117,19 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.005234443913188541</v>
+        <v>-0.1783986615534163</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.2223814134150122</v>
+        <v>0.4204934691467687</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.1645379594759454</v>
+        <v>0.1530775010132241</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,28 +4138,28 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.1263282603943777</v>
+        <v>-0.1703474237331722</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.06835876755868454</v>
+        <v>0.1629615286757252</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.02255074379630192</v>
+        <v>-0.02628007908697251</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
@@ -4171,49 +4171,49 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.09901719993469392</v>
+        <v>-0.2323543921128833</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.05633234275144016</v>
+        <v>0.09357518334109502</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.03488319676408601</v>
+        <v>-0.1595244953703453</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-5.442371515518976e-05</v>
+        <v>-0.08443625558980729</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.1037433025216095</v>
+        <v>0.01187531143744395</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.09908996293241834</v>
+        <v>0.02032933892929783</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
@@ -4225,103 +4225,103 @@
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.06051632405544206</v>
+        <v>-0.02404187668978374</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.04537076372938634</v>
+        <v>-0.1658742329348125</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.0270035482107463</v>
+        <v>-0.1615604875684832</v>
       </c>
       <c r="EB7" t="n">
         <v>0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.1496264211712925</v>
+        <v>-0.165494774416384</v>
       </c>
       <c r="EH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.05408181752017235</v>
+        <v>0.1456877714878389</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.08388441727147807</v>
+        <v>0.007299564638471944</v>
       </c>
       <c r="EK7" t="n">
         <v>0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO7" t="n">
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.1239323094512081</v>
+        <v>-0.129121325504538</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.08859452243650258</v>
+        <v>0.05094923320392247</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.004600190310373539</v>
+        <v>0.004632738071870362</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW7" t="n">
         <v>-0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.1349919399683087</v>
+        <v>-0.2162543237618454</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.03078991228014914</v>
+        <v>0.1886293357380822</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.02655287401859935</v>
+        <v>-0.03955246601223871</v>
       </c>
       <c r="FC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
@@ -4330,82 +4330,82 @@
         <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.01750492248514508</v>
+        <v>-0.137030815688487</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.1183056116134284</v>
+        <v>0.1523905642326349</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.04075974553379428</v>
+        <v>0.05860582381336747</v>
       </c>
       <c r="FL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
         <v>0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.006040215168613386</v>
+        <v>-0.02023192010300329</v>
       </c>
       <c r="FR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.06288928254246694</v>
+        <v>0.05751600892483722</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.001395744075614527</v>
+        <v>0.02989675441637766</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.02933764604954569</v>
+        <v>-0.2115810655009086</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.1421379300947994</v>
+        <v>0.1291639927996125</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
         <v>-0</v>
@@ -4416,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1528130974650531</v>
+        <v>0.2778175108255594</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -4425,16 +4425,16 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.03693996289277889</v>
+        <v>0.009003125346842691</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.09395894013420797</v>
+        <v>-0.03490893113892853</v>
       </c>
       <c r="G8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1601338919073372</v>
+        <v>0.4954761893843489</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -4452,25 +4452,25 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.02928328081058587</v>
+        <v>-0.045685609264107</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2265317519223325</v>
+        <v>-0.03543332614087043</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0189932610829258</v>
+        <v>0.1749741993341282</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -4479,40 +4479,40 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.06479812075311182</v>
+        <v>-0.1480674882606123</v>
       </c>
       <c r="X8" t="n">
-        <v>0.007747083208259673</v>
+        <v>0.04694072411884748</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.02794988254012077</v>
+        <v>0.0315933041699198</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.01173358887217188</v>
+        <v>-0.1799928781663125</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.00398410138929257</v>
+        <v>-0.0572216613356644</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
@@ -4524,25 +4524,25 @@
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.02552666673867286</v>
+        <v>0.2045228285326717</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.02917012903292744</v>
+        <v>0.1191760607326194</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.07869092938714312</v>
+        <v>-0.0827801422966781</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS8" t="n">
         <v>0</v>
@@ -4551,25 +4551,25 @@
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.2464204487608465</v>
+        <v>0.7141583131590958</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.0792562522513614</v>
+        <v>-0.1564399578219964</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.2126722984302099</v>
+        <v>-0.06303715574997307</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
         <v>0</v>
@@ -4578,7 +4578,7 @@
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.02408114919439276</v>
+        <v>-0.02173817420032289</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -4587,52 +4587,52 @@
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.01571616373718141</v>
+        <v>-0.0281203372454846</v>
       </c>
       <c r="BH8" t="n">
-        <v>-3.677102916271438e-11</v>
+        <v>-5.402426457251034e-11</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
         <v>0</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.04281584163265043</v>
+        <v>0.009563680481767797</v>
       </c>
       <c r="BN8" t="n">
         <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.004161993417295017</v>
+        <v>0.0516450026823927</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.01258194869748144</v>
+        <v>-0.01675246842788781</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT8" t="n">
         <v>-0</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.110267786301395</v>
+        <v>0.5399450664196219</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
@@ -4641,16 +4641,16 @@
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.0452070041727554</v>
+        <v>-0.08166004030076959</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.05629454279927943</v>
+        <v>-0.08196420176759991</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
         <v>0</v>
@@ -4659,46 +4659,46 @@
         <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.06433202936961574</v>
+        <v>-0.2354669748267703</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0009328975411003926</v>
+        <v>0.01187671535670083</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.07857605989174679</v>
+        <v>0.06177313993009531</v>
       </c>
       <c r="CJ8" t="n">
         <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0002793374567245274</v>
+        <v>-0.3968153368572812</v>
       </c>
       <c r="CO8" t="n">
         <v>0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.01500214612175427</v>
+        <v>0.2117089663309726</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.04419750925677068</v>
+        <v>0.1819615771077251</v>
       </c>
       <c r="CS8" t="n">
         <v>-0</v>
@@ -4707,40 +4707,40 @@
         <v>-0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
         <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.04621715353624835</v>
+        <v>-0.2187578507781379</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.0124958064246125</v>
+        <v>-0.01234145449708569</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0860141331509905</v>
+        <v>0.04756304956751529</v>
       </c>
       <c r="DB8" t="n">
         <v>0</v>
       </c>
       <c r="DC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.0103193175107484</v>
+        <v>-0.01407352009070974</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
@@ -4749,52 +4749,52 @@
         <v>-0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.1004809256223585</v>
+        <v>-0.2280287962914302</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.05563808213449355</v>
+        <v>0.0627076555919534</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
       </c>
       <c r="DL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.01732054516829446</v>
+        <v>-0.1286491342104563</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
         <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.03545765375535019</v>
+        <v>0.045114769453604</v>
       </c>
       <c r="DS8" t="n">
-        <v>-0.001256302294201263</v>
+        <v>0.002823085815859756</v>
       </c>
       <c r="DT8" t="n">
         <v>0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW8" t="n">
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.001563660292715125</v>
+        <v>0.07082756971739897</v>
       </c>
       <c r="DY8" t="n">
         <v>0</v>
@@ -4803,145 +4803,145 @@
         <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.01520657769052615</v>
+        <v>-0.02281890635208116</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.07875997858308406</v>
+        <v>-0.08355920266976358</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
       </c>
       <c r="ED8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
         <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.05047890721293904</v>
+        <v>-0.02030107604247304</v>
       </c>
       <c r="EH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.009378158950004751</v>
+        <v>-0.1054866400710622</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.04335030519394608</v>
+        <v>-0.01300574840774057</v>
       </c>
       <c r="EL8" t="n">
         <v>-0</v>
       </c>
       <c r="EM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.01623146027242371</v>
+        <v>-0.08220702556058385</v>
       </c>
       <c r="EQ8" t="n">
         <v>-0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.01526312978565387</v>
+        <v>-0.1412173665713972</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.07615706459735753</v>
+        <v>-0.004102706382449348</v>
       </c>
       <c r="EU8" t="n">
         <v>-0</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX8" t="n">
         <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.04322461886049775</v>
+        <v>-0.2355367753010645</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.0009954090060460804</v>
+        <v>-0.0317974822591698</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.07301409903731301</v>
+        <v>0.03871050799418949</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.03412464815305855</v>
+        <v>-0.2341597672612899</v>
       </c>
       <c r="FI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ8" t="n">
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.005591438314509907</v>
+        <v>0.08707689872399707</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.02573030667683497</v>
+        <v>0.08653529649522411</v>
       </c>
       <c r="FM8" t="n">
         <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.0009226235764900416</v>
+        <v>-0.06415150308153142</v>
       </c>
       <c r="FR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS8" t="n">
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.005347345522036847</v>
+        <v>-0.0001252472001393235</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.1048249732957004</v>
+        <v>0.0449498315099178</v>
       </c>
       <c r="FV8" t="n">
         <v>-0</v>
@@ -4950,16 +4950,16 @@
         <v>-0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.02164509513162053</v>
+        <v>-0.1249076314978561</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
         <v>-0</v>
@@ -4968,13 +4968,13 @@
         <v>0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.04024497353545101</v>
+        <v>-0.07447999498438632</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG8" t="n">
         <v>0</v>
@@ -5554,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1229822138409488</v>
+        <v>0.006948662061438373</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -5563,43 +5563,43 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2409138387031231</v>
+        <v>0.0006588177564035692</v>
       </c>
       <c r="F10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.04063152975267617</v>
+        <v>-0.00231084263604896</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.09575028351744122</v>
+        <v>0.01245668357654694</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.353835447785756</v>
+        <v>-0.004281864111118285</v>
       </c>
       <c r="O10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1327360749394213</v>
+        <v>-0.008058712166045305</v>
       </c>
       <c r="R10" t="n">
         <v>-0</v>
@@ -5608,7 +5608,7 @@
         <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2677385288560877</v>
+        <v>0.008171119952147662</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
@@ -5617,34 +5617,34 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1119469456439127</v>
+        <v>-0.006110074734684745</v>
       </c>
       <c r="X10" t="n">
         <v>-0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01602978261646224</v>
+        <v>-0.004239740439033443</v>
       </c>
       <c r="AA10" t="n">
         <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1307345394433382</v>
+        <v>-0.000692225813334754</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.1249163389350802</v>
+        <v>-0.002808133321496467</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -5653,34 +5653,34 @@
         <v>-0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.0300192573445527</v>
+        <v>0.0008803246861593898</v>
       </c>
       <c r="AJ10" t="n">
         <v>-0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.1033039970164462</v>
+        <v>0.006971476760581305</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.1436164659824142</v>
+        <v>0.004857898054177259</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.1446502669575795</v>
+        <v>-0.001371089318053853</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -5689,7 +5689,7 @@
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.4567299099985532</v>
+        <v>0.01789148852856223</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
@@ -5698,16 +5698,16 @@
         <v>-0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.04726912852452538</v>
+        <v>0.001651442249912675</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ10" t="n">
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.2026873964688306</v>
+        <v>-0.005406075015458554</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,7 +5716,7 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.03595314738920357</v>
+        <v>-0.001692335587072649</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -5725,25 +5725,25 @@
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.1245714810615134</v>
+        <v>-0.00429679555900037</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI10" t="n">
         <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-6.756522443169306e-11</v>
+        <v>-5.488700567806289e-13</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
         <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.1385485380508232</v>
+        <v>0.002841486090297017</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
@@ -5752,79 +5752,79 @@
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1235908664390855</v>
+        <v>0.004608543780477848</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.05819372632739497</v>
+        <v>0.002005162402427497</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU10" t="n">
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.2796613804388924</v>
+        <v>0.01318401200484637</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.1111463146142778</v>
+        <v>-0.0004997948308158906</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.1303770405545495</v>
+        <v>-0.007873601471000059</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.08213602999819053</v>
+        <v>-0.002944808660606693</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.09992162316645463</v>
+        <v>-0.001086177736264499</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.03474265307296729</v>
+        <v>0.001716676393937235</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.1661032008767269</v>
+        <v>-0.006294062997154148</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
@@ -5833,34 +5833,34 @@
         <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.2168555208316859</v>
+        <v>0.008510717546176754</v>
       </c>
       <c r="CR10" t="n">
         <v>-0</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>-0.1027102809428309</v>
+        <v>0.001392600154000667</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.0385192218295305</v>
+        <v>-0.002789718503456175</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.04031474723118092</v>
+        <v>-0.0005751216218906784</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
@@ -5869,34 +5869,34 @@
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.02093853165515476</v>
+        <v>0.002735931384430876</v>
       </c>
       <c r="DD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.5338124209660429</v>
+        <v>-0.001463289157547217</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.1606003077353052</v>
+        <v>-0.004457899369525756</v>
       </c>
       <c r="DJ10" t="n">
         <v>0</v>
       </c>
       <c r="DK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0.09213345328699298</v>
+        <v>0.001637064924377763</v>
       </c>
       <c r="DM10" t="n">
         <v>-0</v>
@@ -5905,34 +5905,34 @@
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.03557492027755586</v>
+        <v>-0.006082245057628966</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
         <v>-0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.02205060921058048</v>
+        <v>-0.004431043589474789</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
         <v>0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.002406485321728802</v>
+        <v>0.0002973992020472563</v>
       </c>
       <c r="DV10" t="n">
         <v>-0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.167106062120404</v>
+        <v>0.00433015691420636</v>
       </c>
       <c r="DY10" t="n">
         <v>-0</v>
@@ -5941,34 +5941,34 @@
         <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.03322316265254481</v>
+        <v>-0.001069584682420784</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.0412714120958715</v>
+        <v>-0.005798721521754121</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.1022808332369302</v>
+        <v>0.002183190820799881</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.05242502028520481</v>
+        <v>-0.004790872738758627</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
@@ -5977,25 +5977,25 @@
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.1124616949112452</v>
+        <v>-0.001625419170405609</v>
       </c>
       <c r="EN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.01482138939588701</v>
+        <v>0.0006287752936292688</v>
       </c>
       <c r="EQ10" t="n">
         <v>0</v>
       </c>
       <c r="ER10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.002026911146398636</v>
+        <v>-0.002245388152139618</v>
       </c>
       <c r="ET10" t="n">
         <v>-0</v>
@@ -6004,70 +6004,70 @@
         <v>-0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.1336527542570972</v>
+        <v>0.003144833768614685</v>
       </c>
       <c r="EW10" t="n">
         <v>0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.04939610207260033</v>
+        <v>-0.003408631678527159</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.05604083180215415</v>
+        <v>-0.003091086772132308</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.02919543053692524</v>
+        <v>0.003057653216524924</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.005720656267860572</v>
+        <v>0.0006766241544430911</v>
       </c>
       <c r="FI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.003362826576200152</v>
+        <v>0.004765010864097824</v>
       </c>
       <c r="FL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0.1151592635761048</v>
+        <v>-0.002850354794654169</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
         <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.02115502461460446</v>
+        <v>-0.0005864764638562132</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
@@ -6076,25 +6076,25 @@
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.04560172528840466</v>
+        <v>0.001568094534881969</v>
       </c>
       <c r="FU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV10" t="n">
         <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0.1509575179772978</v>
+        <v>0.005137881611209676</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.1490647639062624</v>
+        <v>-0.005093652686982555</v>
       </c>
       <c r="GA10" t="n">
         <v>0</v>
@@ -6103,69 +6103,69 @@
         <v>-0</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
         <v>-0</v>
       </c>
       <c r="GE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF10" t="n">
-        <v>-0.208191072715553</v>
+        <v>0.001585228831963251</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.1035314883129377</v>
+        <v>-0.06631635266911311</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1434386534238627</v>
+        <v>0.08324328035634648</v>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0620222735469084</v>
+        <v>-0.01156370276765997</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.07631710524818895</v>
+        <v>-0.05684240626888021</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1493180497010315</v>
+        <v>0.1440454973210981</v>
       </c>
       <c r="L11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1860276782735651</v>
+        <v>-0.02032604963548888</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -6174,25 +6174,25 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.02254663328766701</v>
+        <v>0.01679830124926173</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2146746884596998</v>
+        <v>0.02362682532068719</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.229498009933771</v>
+        <v>0.02599860218716693</v>
       </c>
       <c r="X11" t="n">
         <v>-0</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
         <v>-0</v>
@@ -6201,25 +6201,25 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.02170819587950035</v>
+        <v>-0.02112678073286749</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.07904863437530257</v>
+        <v>-0.003880790442857883</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.02055205727581105</v>
+        <v>-0.0321268841653016</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>-0</v>
@@ -6228,10 +6228,10 @@
         <v>-0</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.05994721493981589</v>
+        <v>-0.006067227290891208</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.1190897232102645</v>
+        <v>0.07660973957113296</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -6240,7 +6240,7 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.0598950114210336</v>
+        <v>0.0008626389214105873</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
@@ -6249,43 +6249,43 @@
         <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.2043419933536635</v>
+        <v>0.00119755091791988</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.3519292480427112</v>
+        <v>0.1156741374561227</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.3641205970453783</v>
+        <v>-0.04618910704877682</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>-0.07344350822455496</v>
+        <v>-0.04926657396996659</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.0664261051383027</v>
+        <v>0.0003946042580539253</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.1562578910899388</v>
+        <v>-0.02463506501840929</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
@@ -6309,10 +6309,10 @@
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0.03578024582186944</v>
+        <v>0.01618607446063066</v>
       </c>
       <c r="BM11" t="n">
-        <v>-0.003637054257671612</v>
+        <v>0.01669811272540816</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
@@ -6321,13 +6321,13 @@
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.0777140384845422</v>
+        <v>0.02227362752754249</v>
       </c>
       <c r="BQ11" t="n">
         <v>-0</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
@@ -6336,52 +6336,52 @@
         <v>-0</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.09307390838530667</v>
+        <v>0.01679948405427343</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.2097098760737</v>
+        <v>0.1020588707757626</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.1241732397830629</v>
+        <v>0.008960780681425201</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.01551705184103774</v>
+        <v>0.03828827510050904</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.06399186353352317</v>
+        <v>-0.05764774698360326</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.01871344299276294</v>
+        <v>-0.0003726169812090003</v>
       </c>
       <c r="CI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>-0</v>
@@ -6390,10 +6390,10 @@
         <v>-0</v>
       </c>
       <c r="CM11" t="n">
-        <v>-0.2032963651107543</v>
+        <v>0.006159924246942694</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.04289328548406134</v>
+        <v>-0.08951211151773746</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
@@ -6402,34 +6402,34 @@
         <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.2161702114457638</v>
+        <v>0.0503939565564238</v>
       </c>
       <c r="CR11" t="n">
         <v>-0</v>
       </c>
       <c r="CS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.002083176424512596</v>
+        <v>0.03121307091752654</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.07234344976234799</v>
+        <v>-0.05521308456661996</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.009081691999334831</v>
+        <v>-0.009337652221436649</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
@@ -6444,100 +6444,100 @@
         <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.189467823624617</v>
+        <v>0.01269163770981203</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.2676839332591801</v>
+        <v>-0.082375915515666</v>
       </c>
       <c r="DG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH11" t="n">
         <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.01098598000118707</v>
+        <v>-0.04171518166895653</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
       </c>
       <c r="DL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0.1126939253214247</v>
+        <v>-0.03101954179329904</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.0968391511989613</v>
+        <v>-0.02372099384683216</v>
       </c>
       <c r="DP11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ11" t="n">
         <v>-0</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.0139442611586315</v>
+        <v>0.006291207882172543</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU11" t="n">
         <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW11" t="n">
-        <v>-0.04076194183483746</v>
+        <v>0.04430662409502377</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.1273719348511708</v>
+        <v>0.07674127076146543</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.03381775776219609</v>
+        <v>-0.01615322867664893</v>
       </c>
       <c r="EB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>-0.06287744400266625</v>
+        <v>0.005557651920522546</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.1285789574255333</v>
+        <v>-0.005270567107675204</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
         <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>-0.01312223233488688</v>
+        <v>-0.02557709595662988</v>
       </c>
       <c r="EK11" t="n">
         <v>-0</v>
@@ -6549,22 +6549,22 @@
         <v>-0</v>
       </c>
       <c r="EN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO11" t="n">
-        <v>-0.04215954454276188</v>
+        <v>0.01174738551561584</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.07082537356059614</v>
+        <v>-0.03405961305696294</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.01064021030902394</v>
+        <v>-0.02493471482721616</v>
       </c>
       <c r="ET11" t="n">
         <v>-0</v>
@@ -6573,28 +6573,28 @@
         <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW11" t="n">
         <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.01064314194798258</v>
+        <v>0.04126094752777797</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.07007694132159951</v>
+        <v>-0.06704536432632117</v>
       </c>
       <c r="EZ11" t="n">
         <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.0499737493264616</v>
+        <v>-0.01467588490632529</v>
       </c>
       <c r="FC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD11" t="n">
         <v>-0</v>
@@ -6606,64 +6606,64 @@
         <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.1333920453284312</v>
+        <v>-0.0003647974157029654</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.03570207878727705</v>
+        <v>-0.003655735153709593</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.08545653354199351</v>
+        <v>-0.01451716170819233</v>
       </c>
       <c r="FL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP11" t="n">
-        <v>-0.03659197619569692</v>
+        <v>0.005013721539850234</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.02485179334814884</v>
+        <v>0.008513184087836391</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.008778568758950955</v>
+        <v>0.01785909642180424</v>
       </c>
       <c r="FU11" t="n">
         <v>-0</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX11" t="n">
         <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0.04465902967783031</v>
+        <v>0.02138619519887007</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.1067433823889998</v>
+        <v>-0.05506781219943816</v>
       </c>
       <c r="GA11" t="n">
         <v>-0</v>
@@ -6672,19 +6672,19 @@
         <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF11" t="n">
         <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,25 +6692,25 @@
         <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1967531014800746</v>
+        <v>0.01793999704044621</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1326853381207068</v>
+        <v>-0.009142851235307019</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3211290398153986</v>
+        <v>-0.00877009066830804</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -6719,25 +6719,25 @@
         <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.165548781648796</v>
+        <v>0.03260788844679473</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1617755835416781</v>
+        <v>-0.008754371113593102</v>
       </c>
       <c r="O12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2843924931818344</v>
+        <v>-0.01479423814998852</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -6746,22 +6746,22 @@
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1890178762871751</v>
+        <v>0.002145761910230657</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3014726901464496</v>
+        <v>-0.004020279349070037</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.08932853539769665</v>
+        <v>0.001204697918566161</v>
       </c>
       <c r="Z12" t="n">
         <v>-0</v>
@@ -6773,52 +6773,52 @@
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1215776478147445</v>
+        <v>-0.0007580353619006442</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.04459759572081942</v>
+        <v>-0.01065791703454472</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.02172794533411107</v>
+        <v>0.0001750444096275505</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.03919804754990888</v>
+        <v>0.01748639641325164</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.07364097794090481</v>
+        <v>0.003370503935973913</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.1190187446740823</v>
+        <v>-0.0005777374777606391</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
@@ -6827,7 +6827,7 @@
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.421766026779602</v>
+        <v>0.04641385121494611</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
@@ -6836,16 +6836,16 @@
         <v>-0</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.153457370522545</v>
+        <v>-0.001010340948458038</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.2227265751051482</v>
+        <v>-0.003217833906009205</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
@@ -6854,22 +6854,22 @@
         <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.01172767469822753</v>
+        <v>-0.009943580848575969</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF12" t="n">
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.08975125682950072</v>
+        <v>-0.006594773102848139</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>-0.1125710800223227</v>
+        <v>-0.002433398717868955</v>
       </c>
       <c r="BJ12" t="n">
         <v>0</v>
@@ -6878,25 +6878,25 @@
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.01877406223089849</v>
+        <v>-0.00134990489135423</v>
       </c>
       <c r="BN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO12" t="n">
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1407232078541496</v>
+        <v>0.008601123505241918</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.03635614726881076</v>
+        <v>0.003298856019969289</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6908,49 +6908,49 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1585419320264658</v>
+        <v>0.02620272053552237</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.09418169049096381</v>
+        <v>-0.0007102197017891167</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>-0.1003640260897611</v>
+        <v>0.0002256431838096645</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.09967601038745579</v>
+        <v>-0.0117884523180998</v>
       </c>
       <c r="CF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG12" t="n">
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.06990272080661765</v>
+        <v>0.003015444588166575</v>
       </c>
       <c r="CI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.1001858227767624</v>
+        <v>0.001256760392647451</v>
       </c>
       <c r="CK12" t="n">
         <v>-0</v>
@@ -6959,25 +6959,25 @@
         <v>-0</v>
       </c>
       <c r="CM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.19980019291202</v>
+        <v>-0.02017591505087018</v>
       </c>
       <c r="CO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.1389939320484226</v>
+        <v>0.0004037073374373538</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0.09782187133904673</v>
+        <v>-0.01078961613129431</v>
       </c>
       <c r="CT12" t="n">
         <v>-0</v>
@@ -6986,10 +6986,10 @@
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.08546789253358479</v>
+        <v>-0.0124903031883491</v>
       </c>
       <c r="CX12" t="n">
         <v>-0</v>
@@ -6998,13 +6998,13 @@
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.06381645108872798</v>
+        <v>0.003037658066174946</v>
       </c>
       <c r="DA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.1050539565311575</v>
+        <v>0.003433509499874081</v>
       </c>
       <c r="DC12" t="n">
         <v>0</v>
@@ -7016,7 +7016,7 @@
         <v>-0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.2972857558342821</v>
+        <v>-0.007861910875641828</v>
       </c>
       <c r="DG12" t="n">
         <v>-0</v>
@@ -7025,16 +7025,16 @@
         <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.1056558715535956</v>
+        <v>0.0007340646474303459</v>
       </c>
       <c r="DJ12" t="n">
         <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0.002134122002895079</v>
+        <v>-0.007547189019807958</v>
       </c>
       <c r="DL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM12" t="n">
         <v>0</v>
@@ -7043,34 +7043,34 @@
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.06000136115751147</v>
+        <v>-0.004834857334180209</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.0710827494507628</v>
+        <v>0.005740384600664304</v>
       </c>
       <c r="DS12" t="n">
         <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>-0.02562230405055163</v>
+        <v>0.005650668753257085</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.1221617077709744</v>
+        <v>0.006431364072242055</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
@@ -7079,13 +7079,13 @@
         <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.05097316667809226</v>
+        <v>-0.001464347004562653</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.01469556363085687</v>
+        <v>0.002092321435761929</v>
       </c>
       <c r="ED12" t="n">
         <v>0</v>
@@ -7094,25 +7094,25 @@
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.004459094687092396</v>
+        <v>-0.01168241617915619</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.06952320979517744</v>
+        <v>0.0004574992032435473</v>
       </c>
       <c r="EK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.1185531403638151</v>
+        <v>-0.002871552724256253</v>
       </c>
       <c r="EM12" t="n">
         <v>-0</v>
@@ -7121,10 +7121,10 @@
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.01691113295140781</v>
+        <v>-0.007213000164504053</v>
       </c>
       <c r="EQ12" t="n">
         <v>0</v>
@@ -7133,25 +7133,25 @@
         <v>-0</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.07473611087259915</v>
+        <v>0.001750666986269593</v>
       </c>
       <c r="ET12" t="n">
         <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0.0263561505101442</v>
+        <v>-0.001123204720520667</v>
       </c>
       <c r="EV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW12" t="n">
         <v>-0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.0748555773752909</v>
+        <v>-0.01345227079263396</v>
       </c>
       <c r="EZ12" t="n">
         <v>0</v>
@@ -7160,13 +7160,13 @@
         <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.06765632702235726</v>
+        <v>0.0002056344683772561</v>
       </c>
       <c r="FC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.09000118352020972</v>
+        <v>0.001894505188901299</v>
       </c>
       <c r="FE12" t="n">
         <v>-0</v>
@@ -7175,37 +7175,37 @@
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.05144646514444123</v>
+        <v>-0.003701294631397083</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.08991060884013537</v>
+        <v>-0.003478731070232602</v>
       </c>
       <c r="FL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.06523763630845174</v>
+        <v>-0.001937979295394201</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.004239737072546798</v>
+        <v>-0.001023677170791477</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
@@ -7214,28 +7214,28 @@
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.01645770470849739</v>
+        <v>-0.0008659427995736354</v>
       </c>
       <c r="FU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.01129619207974099</v>
+        <v>0.008231306604833696</v>
       </c>
       <c r="FW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX12" t="n">
         <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.06218959604117497</v>
+        <v>-0.0121541280945356</v>
       </c>
       <c r="GA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB12" t="n">
         <v>-0</v>
@@ -7244,10 +7244,10 @@
         <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.09060746517822918</v>
+        <v>0.008493385868433307</v>
       </c>
       <c r="GF12" t="n">
         <v>-0</v>
@@ -7258,10 +7258,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.3748924275806226</v>
+        <v>0.8309050926186207</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,25 +7270,25 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1600296931432579</v>
+        <v>-0.3316491603508079</v>
       </c>
       <c r="F13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2636693605782814</v>
+        <v>-0.1145965066123604</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2565997018545019</v>
+        <v>1.221191579354656</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,37 +7297,37 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2208555698375181</v>
+        <v>-0.3874795152794828</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.2818136475714852</v>
+        <v>-0.07231988462236469</v>
       </c>
       <c r="S13" t="n">
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.293252484752377</v>
+        <v>0.1195137886804501</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2077271358991394</v>
+        <v>-0.2472919726050109</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
@@ -7336,40 +7336,40 @@
         <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.09864947706528941</v>
+        <v>-0.2352755011029905</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.159484487841386</v>
+        <v>0.08073860188212366</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.05070292838420626</v>
+        <v>-0.1751153503443948</v>
       </c>
       <c r="AG13" t="n">
         <v>-0</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0.0002938793694511098</v>
+        <v>0.01746328733483702</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.1244587901298506</v>
+        <v>0.449723514754974</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
@@ -7378,34 +7378,34 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0488192565820015</v>
+        <v>0.2598468530649321</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>-0.04381008483926356</v>
+        <v>-0.06844526556013927</v>
       </c>
       <c r="AT13" t="n">
         <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.6715782644057747</v>
+        <v>1.494203604874855</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.3136990647440849</v>
+        <v>-0.1789146491423388</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
@@ -7414,16 +7414,16 @@
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0.1962792247247813</v>
+        <v>0.06989984946296865</v>
       </c>
       <c r="BC13" t="n">
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>-0.01891587006125499</v>
+        <v>-0.1695216027853428</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,169 +7432,169 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.1807649580875877</v>
+        <v>-0.2428336498068047</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI13" t="n">
         <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0.1094934051993649</v>
+        <v>-0.04636366757504577</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.02584359099769832</v>
+        <v>0.06051335980238521</v>
       </c>
       <c r="BN13" t="n">
         <v>-0</v>
       </c>
       <c r="BO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.1870568267796834</v>
+        <v>0.1425585168237342</v>
       </c>
       <c r="BQ13" t="n">
         <v>-0</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.01697173789485778</v>
+        <v>0.1017314929142295</v>
       </c>
       <c r="BU13" t="n">
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.3320177746202774</v>
+        <v>0.9647490054869627</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.1465106421526466</v>
+        <v>-0.1958922213627204</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0.07460006742793754</v>
+        <v>-0.1894512413726042</v>
       </c>
       <c r="CD13" t="n">
         <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.1466528737885848</v>
+        <v>-0.5387605841087029</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.0399055460634801</v>
+        <v>0.09240593906609475</v>
       </c>
       <c r="CI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>-0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.1169499566652014</v>
+        <v>0.06857035568529576</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.2139707920251209</v>
+        <v>-0.8097184925702822</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.3114398894456153</v>
+        <v>0.1388241404453169</v>
       </c>
       <c r="CR13" t="n">
         <v>-0</v>
       </c>
       <c r="CS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT13" t="n">
         <v>-0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.01205005100983196</v>
+        <v>0.01941197115203484</v>
       </c>
       <c r="CV13" t="n">
         <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.1360031349537526</v>
+        <v>-0.510063704572951</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.03766796792161418</v>
+        <v>0.06813831608770943</v>
       </c>
       <c r="DA13" t="n">
         <v>0</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.09029879890756654</v>
+        <v>0.1163544892290133</v>
       </c>
       <c r="DE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.4210816563978183</v>
+        <v>-0.1975593874356486</v>
       </c>
       <c r="DG13" t="n">
         <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.1624151967747338</v>
+        <v>0.01246354626715647</v>
       </c>
       <c r="DJ13" t="n">
         <v>-0</v>
@@ -7606,22 +7606,22 @@
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>-0.06814266490793727</v>
+        <v>-0.1322414181978241</v>
       </c>
       <c r="DN13" t="n">
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.07031754336943456</v>
+        <v>-0.3087847648710326</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.01659690399099879</v>
+        <v>0.09815858388612107</v>
       </c>
       <c r="DS13" t="n">
         <v>-0</v>
@@ -7630,25 +7630,25 @@
         <v>0</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.0262764230405947</v>
+        <v>-0.1859692435225738</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.1255972853773169</v>
+        <v>0.3519672798207935</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.03240213912804595</v>
+        <v>-0.1215103611977884</v>
       </c>
       <c r="EB13" t="n">
         <v>-0</v>
@@ -7657,124 +7657,124 @@
         <v>0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.02105052676770558</v>
+        <v>0.1887418934755091</v>
       </c>
       <c r="EF13" t="n">
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.0477550923166057</v>
+        <v>-0.2730735963354937</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
       </c>
       <c r="EI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.007136410342118034</v>
+        <v>-0.03326414170411965</v>
       </c>
       <c r="EK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.1594202455792696</v>
+        <v>0.04872885753864997</v>
       </c>
       <c r="EO13" t="n">
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.05855272667170362</v>
+        <v>-0.3050471594843779</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.03898075593426863</v>
+        <v>0.1048484548855426</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
         <v>-0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0.006983701903096996</v>
+        <v>0.1157698150855133</v>
       </c>
       <c r="EX13" t="n">
         <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.1237692362047819</v>
+        <v>-0.5929048191356148</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.02562664869238359</v>
+        <v>0.04249982178898026</v>
       </c>
       <c r="FC13" t="n">
         <v>-0</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>-0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.08037402790538543</v>
+        <v>0.1168169381621778</v>
       </c>
       <c r="FG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.1785484930258359</v>
+        <v>-0.1762738823524072</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.02555448255386076</v>
+        <v>-0.1626141062353914</v>
       </c>
       <c r="FL13" t="n">
         <v>0</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
         <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>-0.0639965348111458</v>
+        <v>-0.1762213794045218</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.006659230532469761</v>
+        <v>-0.03170433107088848</v>
       </c>
       <c r="FR13" t="n">
         <v>0</v>
@@ -7783,7 +7783,7 @@
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.004814705861240104</v>
+        <v>0.03030047026460708</v>
       </c>
       <c r="FU13" t="n">
         <v>-0</v>
@@ -7795,34 +7795,34 @@
         <v>-0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.01185049018149053</v>
+        <v>-0.1646341342338177</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.1801838169378075</v>
+        <v>-0.2519839808082997</v>
       </c>
       <c r="GA13" t="n">
         <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC13" t="n">
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF13" t="n">
         <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0.01820074221626503</v>
+        <v>0.1027878851715619</v>
       </c>
     </row>
     <row r="14">
@@ -8399,16 +8399,16 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3973942348154369</v>
+        <v>0.3834698145201027</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.3869297454449194</v>
+        <v>-0.201030484460911</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.03790940389189018</v>
+        <v>-0.2002524536706261</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -8417,7 +8417,7 @@
         <v>-0</v>
       </c>
       <c r="H15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -8426,22 +8426,22 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3400307902247467</v>
+        <v>0.5622307396053229</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.3313971157833339</v>
+        <v>-0.2081865583238378</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2845221871196959</v>
+        <v>-0.1899760976538231</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -8453,16 +8453,16 @@
         <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1391847473741506</v>
+        <v>0.08161000077637801</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.020096411284015</v>
+        <v>0.03079324917227349</v>
       </c>
       <c r="V15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.08913288763498137</v>
+        <v>0.136217933474051</v>
       </c>
       <c r="X15" t="n">
         <v>-0</v>
@@ -8471,88 +8471,88 @@
         <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1317712090575189</v>
+        <v>0.030684396803371</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.01141688029956376</v>
+        <v>-0.07412608213264377</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1025289695254997</v>
+        <v>-0.02886722498306664</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ15" t="n">
         <v>-0</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.2731196138523907</v>
+        <v>0.2671830584460315</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0.0764248046762894</v>
+        <v>-0.04300313958705611</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.01160078712098585</v>
+        <v>0.2039564934289614</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT15" t="n">
         <v>-0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.5711124393058232</v>
+        <v>0.6057404644545726</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.2809117076153862</v>
+        <v>0.009722035718835299</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.135602657879228</v>
+        <v>-0.06459203458237972</v>
       </c>
       <c r="AY15" t="n">
         <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB15" t="n">
         <v>-0</v>
@@ -8561,25 +8561,25 @@
         <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.05298625478833106</v>
+        <v>-0.1405034599528169</v>
       </c>
       <c r="BE15" t="n">
-        <v>-0.1902680760816343</v>
+        <v>-0.2227492251446189</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.2066547889677783</v>
+        <v>-0.2138443164854262</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI15" t="n">
         <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
         <v>0</v>
@@ -8588,16 +8588,16 @@
         <v>-0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.0558119573845556</v>
+        <v>0.008027953906426293</v>
       </c>
       <c r="BN15" t="n">
-        <v>-0.04142654980906415</v>
+        <v>-0.0274784874498794</v>
       </c>
       <c r="BO15" t="n">
         <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.1485934867560752</v>
+        <v>0.04516490885037519</v>
       </c>
       <c r="BQ15" t="n">
         <v>-0</v>
@@ -8615,19 +8615,19 @@
         <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.2427362814072155</v>
+        <v>0.4179246889038556</v>
       </c>
       <c r="BW15" t="n">
-        <v>-0.3130440051890404</v>
+        <v>-0.005758323499203948</v>
       </c>
       <c r="BX15" t="n">
         <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.08220227678145035</v>
+        <v>0.05094358285513856</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA15" t="n">
         <v>-0</v>
@@ -8636,31 +8636,31 @@
         <v>0</v>
       </c>
       <c r="CC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD15" t="n">
         <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.127879364943091</v>
+        <v>-0.2582763493398112</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.0559667579442813</v>
+        <v>0.08246593954214139</v>
       </c>
       <c r="CG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.03590423983733948</v>
+        <v>0.07471236145138499</v>
       </c>
       <c r="CI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ15" t="n">
         <v>-0</v>
       </c>
       <c r="CK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL15" t="n">
         <v>-0</v>
@@ -8669,19 +8669,19 @@
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.1256636123743727</v>
+        <v>-0.3608863497855319</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.01351040501228575</v>
+        <v>0.09723922825131422</v>
       </c>
       <c r="CP15" t="n">
         <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.105672133606815</v>
+        <v>0.1519301303225312</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS15" t="n">
         <v>-0</v>
@@ -8690,52 +8690,52 @@
         <v>-0</v>
       </c>
       <c r="CU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV15" t="n">
         <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.08682602841612344</v>
+        <v>-0.2314081720698927</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.05678022934419538</v>
+        <v>0.07534684111931185</v>
       </c>
       <c r="CY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.02676572962776115</v>
+        <v>0.03437154920884211</v>
       </c>
       <c r="DA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB15" t="n">
         <v>0</v>
       </c>
       <c r="DC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD15" t="n">
         <v>0</v>
       </c>
       <c r="DE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.2317707681842975</v>
+        <v>-0.09570286150767271</v>
       </c>
       <c r="DG15" t="n">
-        <v>-0.008385036853769635</v>
+        <v>0.08367640138327626</v>
       </c>
       <c r="DH15" t="n">
         <v>-0</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.08678552100797049</v>
+        <v>0.02634866597721248</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK15" t="n">
         <v>0</v>
@@ -8744,58 +8744,58 @@
         <v>0</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN15" t="n">
         <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.09861715435965021</v>
+        <v>-0.09845526163049413</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.02764301120642342</v>
+        <v>-0.05213191016622843</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.006237634694111434</v>
+        <v>0.08424078051579076</v>
       </c>
       <c r="DS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT15" t="n">
         <v>0</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV15" t="n">
         <v>0</v>
       </c>
       <c r="DW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.03527686750025707</v>
+        <v>0.2631111967593988</v>
       </c>
       <c r="DY15" t="n">
-        <v>-0.04828042541658609</v>
+        <v>0.08068835652237043</v>
       </c>
       <c r="DZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.03552165098889021</v>
+        <v>-0.1608613883925163</v>
       </c>
       <c r="EB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE15" t="n">
         <v>-0</v>
@@ -8804,16 +8804,16 @@
         <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.03517859493527133</v>
+        <v>-0.1398458779139335</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.04455460681110839</v>
+        <v>-0.03059304341447362</v>
       </c>
       <c r="EI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.09401426585957252</v>
+        <v>0.0258143989336397</v>
       </c>
       <c r="EK15" t="n">
         <v>-0</v>
@@ -8825,25 +8825,25 @@
         <v>-0</v>
       </c>
       <c r="EN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.01471588008212446</v>
+        <v>-0.1590956288386185</v>
       </c>
       <c r="EQ15" t="n">
-        <v>-0.07244478847105998</v>
+        <v>0.01125551813924791</v>
       </c>
       <c r="ER15" t="n">
         <v>0</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.07404175784211103</v>
+        <v>0.02805637487883417</v>
       </c>
       <c r="ET15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU15" t="n">
         <v>-0</v>
@@ -8858,16 +8858,16 @@
         <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.109982988053604</v>
+        <v>-0.2678291698541496</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.04412511730973431</v>
+        <v>0.08146182199099408</v>
       </c>
       <c r="FA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.06162960419938292</v>
+        <v>0.04713576193836303</v>
       </c>
       <c r="FC15" t="n">
         <v>-0</v>
@@ -8876,7 +8876,7 @@
         <v>-0</v>
       </c>
       <c r="FE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF15" t="n">
         <v>-0</v>
@@ -8885,70 +8885,70 @@
         <v>-0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.1120737382263909</v>
+        <v>0.002828559858249029</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0.1159226681285526</v>
+        <v>-0.1886087953600304</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.1357887105442148</v>
+        <v>-0.1681780945876827</v>
       </c>
       <c r="FL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM15" t="n">
         <v>0</v>
       </c>
       <c r="FN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP15" t="n">
         <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.0003911510666146346</v>
+        <v>-0.001028425501404971</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.05925453053827907</v>
+        <v>0.03183821994974247</v>
       </c>
       <c r="FS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.01119621909956825</v>
+        <v>0.01707270763177983</v>
       </c>
       <c r="FU15" t="n">
         <v>-0</v>
       </c>
       <c r="FV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.03372937299207063</v>
+        <v>-0.1871516911872305</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.005694079780966347</v>
+        <v>-0.09356792107023043</v>
       </c>
       <c r="GB15" t="n">
         <v>-0</v>
       </c>
       <c r="GC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD15" t="n">
         <v>-0</v>
@@ -8957,10 +8957,10 @@
         <v>-0</v>
       </c>
       <c r="GF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -8968,34 +8968,34 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.5762864846253042</v>
+        <v>1.172569133262698</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.03890766514475855</v>
+        <v>-0.4284659551702766</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H16" t="n">
         <v>-0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4759317514152293</v>
+        <v>-0.2400764310351886</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3616556427490773</v>
+        <v>1.75402790621859</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -9004,7 +9004,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1229495658477554</v>
+        <v>-0.6343249048041675</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -9013,106 +9013,106 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.3955943292618336</v>
+        <v>-0.2320422447631912</v>
       </c>
       <c r="S16" t="n">
         <v>-0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1929463725176761</v>
+        <v>0.136749948800068</v>
       </c>
       <c r="U16" t="n">
         <v>-0</v>
       </c>
       <c r="V16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.09037457748551304</v>
+        <v>-0.1550272621092905</v>
       </c>
       <c r="X16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.1293951059835216</v>
+        <v>-0.2870707741492489</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.1901818142938506</v>
+        <v>-0.001921218248497643</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.02804797771804392</v>
+        <v>-0.152804113763743</v>
       </c>
       <c r="AG16" t="n">
         <v>-0</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0.02776189408480841</v>
+        <v>0.07915634166546699</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.168364891446924</v>
+        <v>0.6095027565818172</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.01778359148451221</v>
+        <v>0.2630991064632814</v>
       </c>
       <c r="AP16" t="n">
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS16" t="n">
-        <v>-0.1290717998328124</v>
+        <v>0.003231463293557187</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.738697678326895</v>
+        <v>1.556348874154071</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
       </c>
       <c r="AW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.3129072956957034</v>
+        <v>-0.3323668186564989</v>
       </c>
       <c r="AY16" t="n">
         <v>-0</v>
@@ -9121,16 +9121,16 @@
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>-0.2229652347246021</v>
+        <v>0.02623806989023438</v>
       </c>
       <c r="BC16" t="n">
         <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.0246301634179462</v>
+        <v>-0.2336493271583848</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
@@ -9139,7 +9139,7 @@
         <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.2306918384119214</v>
+        <v>-0.3274624938816993</v>
       </c>
       <c r="BH16" t="n">
         <v>0</v>
@@ -9148,70 +9148,70 @@
         <v>0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
-        <v>-0.261624289084159</v>
+        <v>-0.163691624238446</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.04522776547214796</v>
+        <v>0.04800428926420198</v>
       </c>
       <c r="BN16" t="n">
         <v>-0</v>
       </c>
       <c r="BO16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.2000299754524568</v>
+        <v>0.1069362165929017</v>
       </c>
       <c r="BQ16" t="n">
         <v>-0</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
         <v>-0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0.007581166424425928</v>
+        <v>0.08430981096300336</v>
       </c>
       <c r="BU16" t="n">
         <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.3898154005329469</v>
+        <v>1.054431385487171</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.1290135926546703</v>
+        <v>-0.2669261968068853</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
       </c>
       <c r="CB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC16" t="n">
-        <v>-0.07549424365451701</v>
+        <v>-0.2302984567350229</v>
       </c>
       <c r="CD16" t="n">
         <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.1475096043755282</v>
+        <v>-0.6367212286858812</v>
       </c>
       <c r="CF16" t="n">
         <v>-0</v>
@@ -9220,25 +9220,25 @@
         <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>-0.00855012581101274</v>
+        <v>0.09776675160683473</v>
       </c>
       <c r="CI16" t="n">
         <v>-0</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
         <v>-0</v>
       </c>
       <c r="CL16" t="n">
-        <v>0.1426260519371196</v>
+        <v>0.08575213874241082</v>
       </c>
       <c r="CM16" t="n">
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.154730930372807</v>
+        <v>-0.9292368484540136</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
@@ -9247,10 +9247,10 @@
         <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.1533088531834239</v>
+        <v>0.2089254070984825</v>
       </c>
       <c r="CR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS16" t="n">
         <v>-0</v>
@@ -9259,40 +9259,40 @@
         <v>-0</v>
       </c>
       <c r="CU16" t="n">
-        <v>-0.04028645221274849</v>
+        <v>-0.007568321049842634</v>
       </c>
       <c r="CV16" t="n">
         <v>0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.128395249650656</v>
+        <v>-0.6086950609373235</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-0.01662642445978228</v>
+        <v>0.02908689832931784</v>
       </c>
       <c r="DA16" t="n">
         <v>0</v>
       </c>
       <c r="DB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>0.1379732716801081</v>
+        <v>0.1637876605727185</v>
       </c>
       <c r="DE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.2436508729366917</v>
+        <v>-0.1052680680062465</v>
       </c>
       <c r="DG16" t="n">
         <v>-0</v>
@@ -9301,7 +9301,7 @@
         <v>-0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.1356746286478605</v>
+        <v>-0.251521147169123</v>
       </c>
       <c r="DJ16" t="n">
         <v>-0</v>
@@ -9313,121 +9313,121 @@
         <v>-0</v>
       </c>
       <c r="DM16" t="n">
-        <v>0.03076126595964385</v>
+        <v>-0.1616350181541067</v>
       </c>
       <c r="DN16" t="n">
         <v>-0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.06262926804449795</v>
+        <v>-0.3365635846880633</v>
       </c>
       <c r="DP16" t="n">
         <v>-0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.02949619350779404</v>
+        <v>0.01528208884236119</v>
       </c>
       <c r="DS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU16" t="n">
         <v>-0</v>
       </c>
       <c r="DV16" t="n">
-        <v>-0.06241216416478299</v>
+        <v>-0.185495901864823</v>
       </c>
       <c r="DW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>0.08962229599118424</v>
+        <v>0.3817402970450439</v>
       </c>
       <c r="DY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA16" t="n">
-        <v>-0.09716709543340471</v>
+        <v>0.006761320419336651</v>
       </c>
       <c r="EB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>0.07421023610202175</v>
+        <v>0.2544303024731683</v>
       </c>
       <c r="EF16" t="n">
         <v>0</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.01648025873368011</v>
+        <v>-0.313804590557994</v>
       </c>
       <c r="EH16" t="n">
         <v>0</v>
       </c>
       <c r="EI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>-0.01789472261514439</v>
+        <v>-0.03750021063220924</v>
       </c>
       <c r="EK16" t="n">
         <v>-0</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
         <v>-0</v>
       </c>
       <c r="EN16" t="n">
-        <v>0.1776237331903701</v>
+        <v>0.04555514194584955</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.09377525029822181</v>
+        <v>-0.3072523616014287</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES16" t="n">
-        <v>-0.0620627267380638</v>
+        <v>0.06127430954501577</v>
       </c>
       <c r="ET16" t="n">
         <v>-0</v>
       </c>
       <c r="EU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW16" t="n">
-        <v>-0.09770718050947881</v>
+        <v>0.1495603384762769</v>
       </c>
       <c r="EX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.1460741456283943</v>
+        <v>-0.6852617535397625</v>
       </c>
       <c r="EZ16" t="n">
         <v>-0</v>
@@ -9436,52 +9436,52 @@
         <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>-0.02957824726279931</v>
+        <v>0.02056503944765502</v>
       </c>
       <c r="FC16" t="n">
         <v>-0</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
         <v>-0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0.1196598748583484</v>
+        <v>0.1669379708929813</v>
       </c>
       <c r="FG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.1350938084890959</v>
+        <v>-0.2945459149721096</v>
       </c>
       <c r="FI16" t="n">
         <v>-0</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>-0.07778084131604002</v>
+        <v>0.005247094171686691</v>
       </c>
       <c r="FL16" t="n">
         <v>0</v>
       </c>
       <c r="FM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO16" t="n">
-        <v>0.03397897109683131</v>
+        <v>0.3665544115776285</v>
       </c>
       <c r="FP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0.0009177178194866802</v>
+        <v>-0.01207876070411418</v>
       </c>
       <c r="FR16" t="n">
         <v>-0</v>
@@ -9490,10 +9490,10 @@
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.002509612902888732</v>
+        <v>0.004562292363596709</v>
       </c>
       <c r="FU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV16" t="n">
         <v>-0</v>
@@ -9502,16 +9502,16 @@
         <v>-0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0.01558381286271588</v>
+        <v>-0.3272759551351537</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0.1570183060808362</v>
+        <v>-0.3304496562400735</v>
       </c>
       <c r="GA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB16" t="n">
         <v>-0</v>
@@ -9520,60 +9520,60 @@
         <v>0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE16" t="n">
         <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG16" t="n">
-        <v>-0.03300752353542719</v>
+        <v>0.2592653410157739</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-0.06196988642427695</v>
+        <v>-0.03324737987029378</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.02157830146126318</v>
+        <v>0.05763767736442159</v>
       </c>
       <c r="C17" t="n">
         <v>-0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02506674382098265</v>
+        <v>-0.02630108228120617</v>
       </c>
       <c r="F17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.02927638035441934</v>
+        <v>-0.02904425470968369</v>
       </c>
       <c r="K17" t="n">
-        <v>0.01523546017741148</v>
+        <v>0.0904240669504679</v>
       </c>
       <c r="L17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.05481414415927063</v>
+        <v>-0.03238125633943145</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9585,121 +9585,121 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.01088172683774266</v>
+        <v>0.006388587210153032</v>
       </c>
       <c r="T17" t="n">
-        <v>0.08543382024462563</v>
+        <v>0.01536801023328587</v>
       </c>
       <c r="U17" t="n">
         <v>-0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1599609714085853</v>
+        <v>0.003162168720786129</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
         <v>-0</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.0294476014271259</v>
+        <v>0.0001486817188154739</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.08273716662724571</v>
+        <v>-0.002077334526655043</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.03154103743629395</v>
+        <v>-0.004479006447694421</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>-0.01846059602208051</v>
+        <v>-0.002062082005981454</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.009584060663724176</v>
+        <v>0.02407235690351322</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.04105705514557742</v>
+        <v>-0.0009076407199388184</v>
       </c>
       <c r="AP17" t="n">
         <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.05023636607146586</v>
+        <v>-0.01273266688742495</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.08569691852753512</v>
+        <v>0.05432145172657275</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
       </c>
       <c r="AW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.2909918467822341</v>
+        <v>-0.02760932032234431</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
         <v>-0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>-0.03264513785238293</v>
+        <v>-0.01883889527312217</v>
       </c>
       <c r="BD17" t="n">
-        <v>-0.06465041751290655</v>
+        <v>0.006769790610030241</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
@@ -9708,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.09699015782562211</v>
+        <v>-0.02194199696819137</v>
       </c>
       <c r="BH17" t="n">
         <v>0</v>
@@ -9720,13 +9720,13 @@
         <v>0</v>
       </c>
       <c r="BK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0.01423960995807043</v>
+        <v>0.0003047334251962463</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.001527692471354151</v>
+        <v>0.004962795780196668</v>
       </c>
       <c r="BN17" t="n">
         <v>-0</v>
@@ -9735,13 +9735,13 @@
         <v>-0</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.05681889136286608</v>
+        <v>0.01919014854124127</v>
       </c>
       <c r="BQ17" t="n">
         <v>-0</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
         <v>-0</v>
@@ -9750,49 +9750,49 @@
         <v>-0</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.03023205923805727</v>
+        <v>0.003512974158480556</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.05592900489319312</v>
+        <v>0.05049634076048325</v>
       </c>
       <c r="BW17" t="n">
         <v>-0</v>
       </c>
       <c r="BX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.1150964028399799</v>
+        <v>-0.00758706807356453</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA17" t="n">
         <v>-0</v>
       </c>
       <c r="CB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD17" t="n">
-        <v>0.01179933562198588</v>
+        <v>0.01506783144595563</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.01085336502574107</v>
+        <v>-0.02289435252511236</v>
       </c>
       <c r="CF17" t="n">
         <v>-0</v>
       </c>
       <c r="CG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.001462645840866377</v>
+        <v>0.00724803832965328</v>
       </c>
       <c r="CI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ17" t="n">
         <v>-0</v>
@@ -9804,10 +9804,10 @@
         <v>-0</v>
       </c>
       <c r="CM17" t="n">
-        <v>-0.05106718600096367</v>
+        <v>0.002273966123341485</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.0611079241242897</v>
+        <v>-0.0481466937333306</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
@@ -9816,25 +9816,25 @@
         <v>0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.1124868329651636</v>
+        <v>0.02287629801199681</v>
       </c>
       <c r="CR17" t="n">
         <v>-0</v>
       </c>
       <c r="CS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
-        <v>-0.0009492113778881295</v>
+        <v>0.01323062092940293</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.01251506067094121</v>
+        <v>-0.02344750137208262</v>
       </c>
       <c r="CX17" t="n">
         <v>0</v>
@@ -9843,10 +9843,10 @@
         <v>0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.01452591249237979</v>
+        <v>0.002677284346959008</v>
       </c>
       <c r="DA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB17" t="n">
         <v>0</v>
@@ -9858,10 +9858,10 @@
         <v>0</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.06086682295206827</v>
+        <v>0.007737460130258346</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.07772794412617097</v>
+        <v>-0.04343351937444222</v>
       </c>
       <c r="DG17" t="n">
         <v>-0</v>
@@ -9870,10 +9870,10 @@
         <v>0</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.005173353103092896</v>
+        <v>-0.00186709233275873</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK17" t="n">
         <v>-0</v>
@@ -9885,10 +9885,10 @@
         <v>-0</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.0275042944629643</v>
+        <v>0.006451161209121972</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.01516190862404751</v>
+        <v>-0.01418403246699374</v>
       </c>
       <c r="DP17" t="n">
         <v>-0</v>
@@ -9897,10 +9897,10 @@
         <v>-0</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.05957509479352951</v>
+        <v>-0.01071193870383904</v>
       </c>
       <c r="DS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT17" t="n">
         <v>0</v>
@@ -9912,10 +9912,10 @@
         <v>-0</v>
       </c>
       <c r="DW17" t="n">
-        <v>-0.01953880749898022</v>
+        <v>0.008890112042103125</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.04347499735805088</v>
+        <v>0.02252121676255159</v>
       </c>
       <c r="DY17" t="n">
         <v>0</v>
@@ -9924,37 +9924,37 @@
         <v>0</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.03471099657373551</v>
+        <v>-0.0009480285719835653</v>
       </c>
       <c r="EB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC17" t="n">
         <v>-0</v>
       </c>
       <c r="ED17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE17" t="n">
         <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>-0.03795272182256001</v>
+        <v>-0.006952360734417991</v>
       </c>
       <c r="EG17" t="n">
-        <v>0.04478016050198617</v>
+        <v>-0.006452725674084806</v>
       </c>
       <c r="EH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.00122687934795023</v>
+        <v>0.0004034962207257726</v>
       </c>
       <c r="EK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL17" t="n">
         <v>-0</v>
@@ -9966,52 +9966,52 @@
         <v>-0</v>
       </c>
       <c r="EO17" t="n">
-        <v>-0.03670340700052688</v>
+        <v>0.007426696615014389</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.0253291772906162</v>
+        <v>-0.001401343791309407</v>
       </c>
       <c r="EQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER17" t="n">
         <v>0</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.01626540013211522</v>
+        <v>-0.008028947070757277</v>
       </c>
       <c r="ET17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV17" t="n">
         <v>-0</v>
       </c>
       <c r="EW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0.01004223450090775</v>
+        <v>0.016353709884531</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.01590452384645929</v>
+        <v>-0.02836055513844557</v>
       </c>
       <c r="EZ17" t="n">
         <v>-0</v>
       </c>
       <c r="FA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB17" t="n">
-        <v>-0.007609554632138853</v>
+        <v>0.002138015446099473</v>
       </c>
       <c r="FC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE17" t="n">
         <v>-0</v>
@@ -10020,10 +10020,10 @@
         <v>-0</v>
       </c>
       <c r="FG17" t="n">
-        <v>0.04831672665354476</v>
+        <v>0.004994422595556261</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.001188273836413377</v>
+        <v>-0.01605886738752538</v>
       </c>
       <c r="FI17" t="n">
         <v>-0</v>
@@ -10032,13 +10032,13 @@
         <v>-0</v>
       </c>
       <c r="FK17" t="n">
-        <v>-0.04354743906506168</v>
+        <v>0.02202174877038119</v>
       </c>
       <c r="FL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN17" t="n">
         <v>0</v>
@@ -10047,25 +10047,25 @@
         <v>-0</v>
       </c>
       <c r="FP17" t="n">
-        <v>-0.00864116376108167</v>
+        <v>0.007011289214461922</v>
       </c>
       <c r="FQ17" t="n">
-        <v>-0.008574872268035435</v>
+        <v>0.0006965244908051751</v>
       </c>
       <c r="FR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS17" t="n">
         <v>-0</v>
       </c>
       <c r="FT17" t="n">
-        <v>-0.002735115164954084</v>
+        <v>0.002836364447147051</v>
       </c>
       <c r="FU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW17" t="n">
         <v>-0</v>
@@ -10074,10 +10074,10 @@
         <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>0.00888792625087515</v>
+        <v>0.01709407451996895</v>
       </c>
       <c r="FZ17" t="n">
-        <v>-0.05785661319273946</v>
+        <v>-0.01563696377184099</v>
       </c>
       <c r="GA17" t="n">
         <v>-0</v>
@@ -10086,19 +10086,19 @@
         <v>-0</v>
       </c>
       <c r="GC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF17" t="n">
         <v>-0</v>
       </c>
       <c r="GG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -10106,22 +10106,22 @@
         <v>-0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.6230967947377091</v>
+        <v>0.1150811733497091</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2298679050068682</v>
+        <v>-0.138435503802332</v>
       </c>
       <c r="F18" t="n">
         <v>-0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2820834855257625</v>
+        <v>-0.03817525274268064</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -10130,25 +10130,25 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4304934126226094</v>
+        <v>0.1351041272283474</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2280450499249365</v>
+        <v>-0.1957355380700311</v>
       </c>
       <c r="O18" t="n">
         <v>-0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.26982065162152</v>
+        <v>-0.09020807403320612</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -10160,22 +10160,22 @@
         <v>-0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.191800523883264</v>
+        <v>0.1057245152351827</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V18" t="n">
         <v>-0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2035317511841458</v>
+        <v>0.01904991393067623</v>
       </c>
       <c r="X18" t="n">
         <v>-0</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.03749990901794777</v>
+        <v>0.024801540417515</v>
       </c>
       <c r="Z18" t="n">
         <v>-0</v>
@@ -10187,34 +10187,34 @@
         <v>-0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.1213707186713641</v>
+        <v>-0.02564045810488582</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.02297303035666883</v>
+        <v>-0.05312266086009543</v>
       </c>
       <c r="AG18" t="n">
         <v>-0</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.03468184944527334</v>
+        <v>0.02488460393084486</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.04788546795323805</v>
+        <v>0.1624147672178092</v>
       </c>
       <c r="AM18" t="n">
         <v>-0</v>
@@ -10223,25 +10223,25 @@
         <v>-0</v>
       </c>
       <c r="AO18" t="n">
-        <v>5.37015813304472e-05</v>
+        <v>0.06832405251154929</v>
       </c>
       <c r="AP18" t="n">
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>-0.04857311865628243</v>
+        <v>-0.0101929374315547</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT18" t="n">
         <v>-0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.5953409381712609</v>
+        <v>0.2753537360716661</v>
       </c>
       <c r="AV18" t="n">
         <v>-0</v>
@@ -10250,13 +10250,13 @@
         <v>-0</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.03351199170197187</v>
+        <v>0.01576569524542622</v>
       </c>
       <c r="AY18" t="n">
         <v>-0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>-0.1949717368598288</v>
+        <v>-0.004000673472177927</v>
       </c>
       <c r="BA18" t="n">
         <v>0</v>
@@ -10265,37 +10265,37 @@
         <v>-0</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.1137639605539935</v>
+        <v>-0.1815370409322398</v>
       </c>
       <c r="BE18" t="n">
         <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.04904333510552822</v>
+        <v>-0.1305148422245813</v>
       </c>
       <c r="BH18" t="n">
         <v>-0</v>
       </c>
       <c r="BI18" t="n">
-        <v>-0.1316065033536127</v>
+        <v>-0.02790785290046986</v>
       </c>
       <c r="BJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK18" t="n">
         <v>0</v>
       </c>
       <c r="BL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.03277272858928144</v>
+        <v>-0.009859537281163922</v>
       </c>
       <c r="BN18" t="n">
         <v>0</v>
@@ -10304,13 +10304,13 @@
         <v>-0</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.09388099831453235</v>
+        <v>0.05746035325305048</v>
       </c>
       <c r="BQ18" t="n">
         <v>-0</v>
       </c>
       <c r="BR18" t="n">
-        <v>-0.02109362160485066</v>
+        <v>0.04299597496953666</v>
       </c>
       <c r="BS18" t="n">
         <v>-0</v>
@@ -10322,34 +10322,34 @@
         <v>-0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.2670656460320763</v>
+        <v>0.2702322459380378</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>-0.02527612372531163</v>
+        <v>-0.01477965657887461</v>
       </c>
       <c r="BZ18" t="n">
         <v>-0</v>
       </c>
       <c r="CA18" t="n">
-        <v>-0.09509320445147235</v>
+        <v>0.005003105961872338</v>
       </c>
       <c r="CB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.1480972029530638</v>
+        <v>-0.07825110778490374</v>
       </c>
       <c r="CF18" t="n">
         <v>0</v>
@@ -10358,13 +10358,13 @@
         <v>-0</v>
       </c>
       <c r="CH18" t="n">
-        <v>0.05179862296726951</v>
+        <v>0.04512445521393275</v>
       </c>
       <c r="CI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ18" t="n">
-        <v>0.09273083570616583</v>
+        <v>0.01492846060415177</v>
       </c>
       <c r="CK18" t="n">
         <v>-0</v>
@@ -10373,25 +10373,25 @@
         <v>-0</v>
       </c>
       <c r="CM18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN18" t="n">
-        <v>-0.1487842492830839</v>
+        <v>-0.1310524922290528</v>
       </c>
       <c r="CO18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP18" t="n">
         <v>-0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-0.2357595886604433</v>
+        <v>0.01558881685733154</v>
       </c>
       <c r="CR18" t="n">
         <v>0</v>
       </c>
       <c r="CS18" t="n">
-        <v>0.01925027512181046</v>
+        <v>-0.001164431036933624</v>
       </c>
       <c r="CT18" t="n">
         <v>-0</v>
@@ -10400,25 +10400,25 @@
         <v>-0</v>
       </c>
       <c r="CV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.1313777165830904</v>
+        <v>-0.06834819505910046</v>
       </c>
       <c r="CX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY18" t="n">
         <v>0</v>
       </c>
       <c r="CZ18" t="n">
-        <v>0.04534936228162343</v>
+        <v>0.04185893679375527</v>
       </c>
       <c r="DA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB18" t="n">
-        <v>0.07737523150409632</v>
+        <v>0.02470893585465375</v>
       </c>
       <c r="DC18" t="n">
         <v>0</v>
@@ -10427,10 +10427,10 @@
         <v>0</v>
       </c>
       <c r="DE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF18" t="n">
-        <v>-0.3791234653902477</v>
+        <v>-0.09828673281553542</v>
       </c>
       <c r="DG18" t="n">
         <v>-0</v>
@@ -10439,25 +10439,25 @@
         <v>-0</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.05732061726185823</v>
+        <v>0.02004517283929807</v>
       </c>
       <c r="DJ18" t="n">
         <v>-0</v>
       </c>
       <c r="DK18" t="n">
-        <v>-0.03069634081658408</v>
+        <v>-0.03967674557905392</v>
       </c>
       <c r="DL18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM18" t="n">
         <v>-0</v>
       </c>
       <c r="DN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.03087263724140537</v>
+        <v>0.00966242393243511</v>
       </c>
       <c r="DP18" t="n">
         <v>0</v>
@@ -10466,25 +10466,25 @@
         <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.03538483537038278</v>
+        <v>0.03014031611070733</v>
       </c>
       <c r="DS18" t="n">
         <v>-0</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.04982342247037403</v>
+        <v>0.008946065406558306</v>
       </c>
       <c r="DU18" t="n">
         <v>-0</v>
       </c>
       <c r="DV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX18" t="n">
-        <v>0.1848274693132345</v>
+        <v>0.08836675048966633</v>
       </c>
       <c r="DY18" t="n">
         <v>-0</v>
@@ -10493,13 +10493,13 @@
         <v>-0</v>
       </c>
       <c r="EA18" t="n">
-        <v>-0.07529051587909213</v>
+        <v>-0.07716692998418799</v>
       </c>
       <c r="EB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC18" t="n">
-        <v>-0.01287478347515655</v>
+        <v>-0.03958318969481712</v>
       </c>
       <c r="ED18" t="n">
         <v>0</v>
@@ -10508,25 +10508,25 @@
         <v>-0</v>
       </c>
       <c r="EF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.08677472207684624</v>
+        <v>-0.05775212001860885</v>
       </c>
       <c r="EH18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.05349673734721461</v>
+        <v>0.03279112757518322</v>
       </c>
       <c r="EK18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL18" t="n">
-        <v>0.07405967565302851</v>
+        <v>-0.007535349749458635</v>
       </c>
       <c r="EM18" t="n">
         <v>-0</v>
@@ -10535,10 +10535,10 @@
         <v>-0</v>
       </c>
       <c r="EO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP18" t="n">
-        <v>-0.04985286739500946</v>
+        <v>-0.08400115148792793</v>
       </c>
       <c r="EQ18" t="n">
         <v>0</v>
@@ -10547,13 +10547,13 @@
         <v>-0</v>
       </c>
       <c r="ES18" t="n">
-        <v>0.08951555307311523</v>
+        <v>-0.0007415300089427936</v>
       </c>
       <c r="ET18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU18" t="n">
-        <v>-0.02328310853147835</v>
+        <v>0.01466141432996746</v>
       </c>
       <c r="EV18" t="n">
         <v>-0</v>
@@ -10562,10 +10562,10 @@
         <v>0</v>
       </c>
       <c r="EX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.1368774920141322</v>
+        <v>-0.07511641651166935</v>
       </c>
       <c r="EZ18" t="n">
         <v>0</v>
@@ -10574,13 +10574,13 @@
         <v>-0</v>
       </c>
       <c r="FB18" t="n">
-        <v>0.03664759987736995</v>
+        <v>0.02970551940811302</v>
       </c>
       <c r="FC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD18" t="n">
-        <v>0.06394544505623938</v>
+        <v>0.01277197932692583</v>
       </c>
       <c r="FE18" t="n">
         <v>-0</v>
@@ -10592,22 +10592,22 @@
         <v>-0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.03636547257537714</v>
+        <v>-0.007555595906666345</v>
       </c>
       <c r="FI18" t="n">
         <v>-0</v>
       </c>
       <c r="FJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK18" t="n">
-        <v>-0.1273792857152878</v>
+        <v>-0.03332271893902943</v>
       </c>
       <c r="FL18" t="n">
         <v>-0</v>
       </c>
       <c r="FM18" t="n">
-        <v>0.03767809393922305</v>
+        <v>-0.01552756431481995</v>
       </c>
       <c r="FN18" t="n">
         <v>-0</v>
@@ -10616,10 +10616,10 @@
         <v>-0</v>
       </c>
       <c r="FP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>-0.01717440346216871</v>
+        <v>-0.01039366530383102</v>
       </c>
       <c r="FR18" t="n">
         <v>-0</v>
@@ -10628,28 +10628,28 @@
         <v>-0</v>
       </c>
       <c r="FT18" t="n">
-        <v>0.01029687013559413</v>
+        <v>-0.001032079426912844</v>
       </c>
       <c r="FU18" t="n">
         <v>0</v>
       </c>
       <c r="FV18" t="n">
-        <v>0.005251585258958837</v>
+        <v>-0.05919270081629275</v>
       </c>
       <c r="FW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX18" t="n">
         <v>-0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>-0.05666086010276626</v>
+        <v>-0.095903902371884</v>
       </c>
       <c r="GA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB18" t="n">
         <v>-0</v>
@@ -10658,16 +10658,16 @@
         <v>0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE18" t="n">
-        <v>0.006245253610043608</v>
+        <v>0.005786886733725597</v>
       </c>
       <c r="GF18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -11241,19 +11241,19 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B20" t="n">
-        <v>1.122018135945418</v>
+        <v>0.5637218027403765</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.72465548038176</v>
+        <v>-0.2125896642526773</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2558599638236534</v>
+        <v>-0.1147439786754287</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -11268,79 +11268,79 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8362153934633199</v>
+        <v>0.4247957767308129</v>
       </c>
       <c r="L20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7469482146103525</v>
+        <v>-0.4216502986871287</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3943593797744863</v>
+        <v>-0.2624015930611194</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P20" t="n">
         <v>-0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2259741927475408</v>
+        <v>0.2296230524109054</v>
       </c>
       <c r="U20" t="n">
         <v>-0</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.07609352016450691</v>
+        <v>-0.1139162025291348</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.03924317122833348</v>
+        <v>0.009073427450176809</v>
       </c>
       <c r="X20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
         <v>-0</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.194783481884282</v>
+        <v>-0.0005256093954026516</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.003586845556899911</v>
+        <v>-0.1444702487150704</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.02052064499101308</v>
+        <v>-0.06600595553115686</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>-0</v>
@@ -11352,22 +11352,22 @@
         <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.1445423324936787</v>
+        <v>0.3883864987530875</v>
       </c>
       <c r="AM20" t="n">
         <v>-0</v>
       </c>
       <c r="AN20" t="n">
-        <v>-0.07959609397330283</v>
+        <v>-0.02616689020282556</v>
       </c>
       <c r="AO20" t="n">
-        <v>-0.03648801437920302</v>
+        <v>0.2781604200332985</v>
       </c>
       <c r="AP20" t="n">
         <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
         <v>-0</v>
@@ -11379,16 +11379,16 @@
         <v>-0</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.9402861821531056</v>
+        <v>0.650590977346121</v>
       </c>
       <c r="AV20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>-0.04677021835653954</v>
+        <v>-0.06621182154908616</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.2058068607049598</v>
+        <v>-0.2357300842396405</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
@@ -11400,58 +11400,58 @@
         <v>-0</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC20" t="n">
         <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>0.1507948866918256</v>
+        <v>-0.2384727476946981</v>
       </c>
       <c r="BE20" t="n">
         <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>-0.4073670240154573</v>
+        <v>-0.1364694184519236</v>
       </c>
       <c r="BG20" t="n">
-        <v>-0.4437829920915622</v>
+        <v>-0.1530817261321012</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK20" t="n">
         <v>0</v>
       </c>
       <c r="BL20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.1112104282094023</v>
+        <v>-0.06548006804571165</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.02840549735895314</v>
+        <v>-0.005084286635698981</v>
       </c>
       <c r="BP20" t="n">
-        <v>0.09788005661191661</v>
+        <v>0.01099043897982945</v>
       </c>
       <c r="BQ20" t="n">
         <v>-0</v>
       </c>
       <c r="BR20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT20" t="n">
         <v>-0</v>
@@ -11460,25 +11460,25 @@
         <v>-0</v>
       </c>
       <c r="BV20" t="n">
-        <v>0.4833785079748268</v>
+        <v>0.4869933014666402</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>-0.070018744174022</v>
+        <v>-0.2347423752966413</v>
       </c>
       <c r="BY20" t="n">
-        <v>0.006494526432973929</v>
+        <v>-0.1119854364325178</v>
       </c>
       <c r="BZ20" t="n">
         <v>0</v>
       </c>
       <c r="CA20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC20" t="n">
         <v>0</v>
@@ -11487,43 +11487,43 @@
         <v>-0</v>
       </c>
       <c r="CE20" t="n">
-        <v>-0.212487994096229</v>
+        <v>-0.2055644401113055</v>
       </c>
       <c r="CF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG20" t="n">
-        <v>0.145759408781161</v>
+        <v>0.0805427015488339</v>
       </c>
       <c r="CH20" t="n">
-        <v>-0.02777398623753819</v>
+        <v>0.01382227659326587</v>
       </c>
       <c r="CI20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ20" t="n">
         <v>-0</v>
       </c>
       <c r="CK20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM20" t="n">
         <v>0</v>
       </c>
       <c r="CN20" t="n">
-        <v>-0.07520934244225654</v>
+        <v>-0.2003830941842263</v>
       </c>
       <c r="CO20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP20" t="n">
-        <v>-0.1608683995276499</v>
+        <v>0.2986862801863343</v>
       </c>
       <c r="CQ20" t="n">
-        <v>-0.1775480390020512</v>
+        <v>0.3176440993315223</v>
       </c>
       <c r="CR20" t="n">
         <v>0</v>
@@ -11538,22 +11538,22 @@
         <v>-0</v>
       </c>
       <c r="CV20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW20" t="n">
-        <v>-0.1862221926442347</v>
+        <v>-0.2002417262548023</v>
       </c>
       <c r="CX20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY20" t="n">
-        <v>0.1808820917870373</v>
+        <v>0.1099511816231972</v>
       </c>
       <c r="CZ20" t="n">
-        <v>-0.03032411919529011</v>
+        <v>0.03672508340548285</v>
       </c>
       <c r="DA20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB20" t="n">
         <v>0</v>
@@ -11562,25 +11562,25 @@
         <v>-0</v>
       </c>
       <c r="DD20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE20" t="n">
         <v>0</v>
       </c>
       <c r="DF20" t="n">
-        <v>-0.09471873216513918</v>
+        <v>-0.1270964887434559</v>
       </c>
       <c r="DG20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH20" t="n">
-        <v>0.1338171315498503</v>
+        <v>0.1362878852944327</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.04740552393662056</v>
+        <v>0.007370611229451239</v>
       </c>
       <c r="DJ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK20" t="n">
         <v>-0</v>
@@ -11589,25 +11589,25 @@
         <v>0</v>
       </c>
       <c r="DM20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN20" t="n">
         <v>-0</v>
       </c>
       <c r="DO20" t="n">
-        <v>-0.09314855854594296</v>
+        <v>-0.07096788675751922</v>
       </c>
       <c r="DP20" t="n">
         <v>0</v>
       </c>
       <c r="DQ20" t="n">
-        <v>0.02988926805507364</v>
+        <v>0.01249294757707037</v>
       </c>
       <c r="DR20" t="n">
-        <v>-0.04886128582793264</v>
+        <v>-0.009678781368001769</v>
       </c>
       <c r="DS20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT20" t="n">
         <v>-0</v>
@@ -11622,25 +11622,25 @@
         <v>-0</v>
       </c>
       <c r="DX20" t="n">
-        <v>0.06074729547891081</v>
+        <v>0.1955981464465295</v>
       </c>
       <c r="DY20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ20" t="n">
-        <v>0.01166151118401699</v>
+        <v>0.104954910287534</v>
       </c>
       <c r="EA20" t="n">
-        <v>0.01382198848730749</v>
+        <v>-0.03590648321385174</v>
       </c>
       <c r="EB20" t="n">
         <v>0</v>
       </c>
       <c r="EC20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE20" t="n">
         <v>-0</v>
@@ -11649,16 +11649,16 @@
         <v>0</v>
       </c>
       <c r="EG20" t="n">
-        <v>-0.1313408581523442</v>
+        <v>-0.2041185092129816</v>
       </c>
       <c r="EH20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI20" t="n">
-        <v>0.1018752148760113</v>
+        <v>0.03719520913847092</v>
       </c>
       <c r="EJ20" t="n">
-        <v>0.1120847538029157</v>
+        <v>0.0007425153571658991</v>
       </c>
       <c r="EK20" t="n">
         <v>0</v>
@@ -11667,7 +11667,7 @@
         <v>-0</v>
       </c>
       <c r="EM20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN20" t="n">
         <v>-0</v>
@@ -11676,22 +11676,22 @@
         <v>0</v>
       </c>
       <c r="EP20" t="n">
-        <v>-0.1381966460211396</v>
+        <v>-0.1033459660738225</v>
       </c>
       <c r="EQ20" t="n">
         <v>0</v>
       </c>
       <c r="ER20" t="n">
-        <v>0.150038000935677</v>
+        <v>0.07723900619466535</v>
       </c>
       <c r="ES20" t="n">
-        <v>-0.1036998451407754</v>
+        <v>-0.0800696698998917</v>
       </c>
       <c r="ET20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV20" t="n">
         <v>0</v>
@@ -11703,19 +11703,19 @@
         <v>0</v>
       </c>
       <c r="EY20" t="n">
-        <v>-0.1941905612275904</v>
+        <v>-0.2436004913229866</v>
       </c>
       <c r="EZ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA20" t="n">
-        <v>0.1765661860977534</v>
+        <v>0.1280177877744421</v>
       </c>
       <c r="FB20" t="n">
-        <v>-0.0256057164758392</v>
+        <v>0.02670773976773904</v>
       </c>
       <c r="FC20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD20" t="n">
         <v>-0</v>
@@ -11724,49 +11724,49 @@
         <v>0</v>
       </c>
       <c r="FF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG20" t="n">
         <v>0</v>
       </c>
       <c r="FH20" t="n">
-        <v>-0.0775105639630673</v>
+        <v>-0.07221577918718651</v>
       </c>
       <c r="FI20" t="n">
         <v>-0</v>
       </c>
       <c r="FJ20" t="n">
-        <v>-0.1421335572945441</v>
+        <v>-0.07717472623672304</v>
       </c>
       <c r="FK20" t="n">
-        <v>0.01368691822933432</v>
+        <v>0.05661294358514878</v>
       </c>
       <c r="FL20" t="n">
         <v>-0</v>
       </c>
       <c r="FM20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ20" t="n">
-        <v>0.01749966437096402</v>
+        <v>-0.1669839163458794</v>
       </c>
       <c r="FR20" t="n">
         <v>-0</v>
       </c>
       <c r="FS20" t="n">
-        <v>0.06403229648193491</v>
+        <v>0.1326674392689343</v>
       </c>
       <c r="FT20" t="n">
-        <v>-0.02771869302806579</v>
+        <v>0.04863713899351528</v>
       </c>
       <c r="FU20" t="n">
         <v>-0</v>
@@ -11781,28 +11781,28 @@
         <v>0</v>
       </c>
       <c r="FY20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ20" t="n">
-        <v>-0.03990372955609502</v>
+        <v>-0.2228015631947963</v>
       </c>
       <c r="GA20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB20" t="n">
-        <v>-0.03757713772222909</v>
+        <v>0.03571015329852262</v>
       </c>
       <c r="GC20" t="n">
         <v>0</v>
       </c>
       <c r="GD20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE20" t="n">
         <v>-0</v>
       </c>
       <c r="GF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG20" t="n">
         <v>-0</v>
@@ -12379,19 +12379,19 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.2135711778184812</v>
+        <v>0.1894507845402688</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.0200375751937938</v>
+        <v>-0.1639065130793105</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.01460281628765668</v>
+        <v>-0.04264270854594269</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.08285217580689934</v>
+        <v>0.06230444525620497</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -12400,25 +12400,25 @@
         <v>-0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I22" t="n">
         <v>-0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1958969370354255</v>
+        <v>0.1480583784256024</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.01657921299640375</v>
+        <v>-0.2521131568654864</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.03858097951454405</v>
+        <v>-0.09107013080609139</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.03309122734648359</v>
+        <v>0.07509490605240414</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -12427,58 +12427,58 @@
         <v>-0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R22" t="n">
         <v>-0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.01752097074688871</v>
+        <v>-7.845257226329966e-06</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0156089902171183</v>
+        <v>-0.004636590231535003</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V22" t="n">
-        <v>0.008127315115950438</v>
+        <v>0.01531728540141345</v>
       </c>
       <c r="W22" t="n">
-        <v>0.03970486758962213</v>
+        <v>-0.007073715189541386</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
         <v>-0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.03576379762076647</v>
+        <v>0.06536047092622864</v>
       </c>
       <c r="AC22" t="n">
-        <v>-0.008225516785652847</v>
+        <v>0.02391807206832636</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.07148000618522449</v>
+        <v>0.1217405318087628</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.03490082111419569</v>
+        <v>0.0860385629833178</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -12487,19 +12487,19 @@
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.01682594728653442</v>
+        <v>0.02186957544017005</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.01030297017267876</v>
+        <v>-0.08375454127631253</v>
       </c>
       <c r="AM22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>0.004583854871728047</v>
+        <v>-0.01008372716230121</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.00769052051254668</v>
+        <v>-0.05977241081396918</v>
       </c>
       <c r="AP22" t="n">
         <v>-0</v>
@@ -12508,25 +12508,25 @@
         <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.1216549328214886</v>
+        <v>-0.02917710151201972</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.020790855197893</v>
+        <v>-0.2011811800886015</v>
       </c>
       <c r="AV22" t="n">
         <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>-0.04025759710404005</v>
+        <v>-0.1253720717359566</v>
       </c>
       <c r="AX22" t="n">
-        <v>-0.1054946395555711</v>
+        <v>-0.03590450871955744</v>
       </c>
       <c r="AY22" t="n">
         <v>-0</v>
@@ -12535,193 +12535,193 @@
         <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC22" t="n">
-        <v>0.07619849637123111</v>
+        <v>0.06272759495903087</v>
       </c>
       <c r="BD22" t="n">
-        <v>0.005922280834923556</v>
+        <v>-0.03274936706706261</v>
       </c>
       <c r="BE22" t="n">
         <v>-0</v>
       </c>
       <c r="BF22" t="n">
-        <v>-0.004316768489017265</v>
+        <v>0.1228775022112861</v>
       </c>
       <c r="BG22" t="n">
-        <v>-0.02917589206054888</v>
+        <v>0.04383349536257192</v>
       </c>
       <c r="BH22" t="n">
         <v>0</v>
       </c>
       <c r="BI22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL22" t="n">
-        <v>0.02662714387007606</v>
+        <v>-0.01398485056700761</v>
       </c>
       <c r="BM22" t="n">
-        <v>-0.01049971776171234</v>
+        <v>0.01579930654047258</v>
       </c>
       <c r="BN22" t="n">
         <v>-0</v>
       </c>
       <c r="BO22" t="n">
-        <v>0.0073598326182158</v>
+        <v>-0.005641969372640524</v>
       </c>
       <c r="BP22" t="n">
-        <v>-0.01131316258403067</v>
+        <v>-0.08352592994026853</v>
       </c>
       <c r="BQ22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT22" t="n">
         <v>0</v>
       </c>
       <c r="BU22" t="n">
-        <v>0.06105203029611198</v>
+        <v>-0.0283044800042095</v>
       </c>
       <c r="BV22" t="n">
-        <v>-0.0529908366516541</v>
+        <v>-0.1762359509566682</v>
       </c>
       <c r="BW22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX22" t="n">
-        <v>-0.01501081431717462</v>
+        <v>-0.1250043978464087</v>
       </c>
       <c r="BY22" t="n">
-        <v>-0.02950809935372148</v>
+        <v>-0.02446523250980522</v>
       </c>
       <c r="BZ22" t="n">
         <v>-0</v>
       </c>
       <c r="CA22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB22" t="n">
         <v>-0</v>
       </c>
       <c r="CC22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD22" t="n">
-        <v>-0.03729698418428855</v>
+        <v>-0.05563699213246081</v>
       </c>
       <c r="CE22" t="n">
-        <v>-0.01303369108681982</v>
+        <v>0.08942698752331207</v>
       </c>
       <c r="CF22" t="n">
         <v>0</v>
       </c>
       <c r="CG22" t="n">
-        <v>-0.01085701310433764</v>
+        <v>0.04461753074618681</v>
       </c>
       <c r="CH22" t="n">
-        <v>0.00414052422348728</v>
+        <v>-0.02984144365579219</v>
       </c>
       <c r="CI22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL22" t="n">
         <v>0</v>
       </c>
       <c r="CM22" t="n">
-        <v>-0.01832499063553694</v>
+        <v>0.1160426740112251</v>
       </c>
       <c r="CN22" t="n">
-        <v>-0.05298165274978874</v>
+        <v>0.1837901431892057</v>
       </c>
       <c r="CO22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP22" t="n">
-        <v>0.05332479755548703</v>
+        <v>0.1698616362132518</v>
       </c>
       <c r="CQ22" t="n">
-        <v>0.03983679069299052</v>
+        <v>0.01659281711895302</v>
       </c>
       <c r="CR22" t="n">
         <v>0</v>
       </c>
       <c r="CS22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV22" t="n">
-        <v>-0.02965199369025286</v>
+        <v>-0.03913946488339157</v>
       </c>
       <c r="CW22" t="n">
-        <v>-0.008419522162224472</v>
+        <v>0.07949644082659262</v>
       </c>
       <c r="CX22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY22" t="n">
-        <v>-0.004093893869927957</v>
+        <v>0.04978549166968368</v>
       </c>
       <c r="CZ22" t="n">
-        <v>0.01384432608639536</v>
+        <v>-0.02499515751680768</v>
       </c>
       <c r="DA22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB22" t="n">
         <v>-0</v>
       </c>
       <c r="DC22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD22" t="n">
         <v>-0</v>
       </c>
       <c r="DE22" t="n">
-        <v>-0.01510663362511595</v>
+        <v>0.03587189638098578</v>
       </c>
       <c r="DF22" t="n">
-        <v>0.04785650869952162</v>
+        <v>0.03513180222437939</v>
       </c>
       <c r="DG22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH22" t="n">
-        <v>0.02332664571453313</v>
+        <v>-0.002440562409562977</v>
       </c>
       <c r="DI22" t="n">
-        <v>-0.07718974611088744</v>
+        <v>0.0401453157442435</v>
       </c>
       <c r="DJ22" t="n">
         <v>0</v>
       </c>
       <c r="DK22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL22" t="n">
         <v>0</v>
@@ -12730,79 +12730,79 @@
         <v>0</v>
       </c>
       <c r="DN22" t="n">
-        <v>-0.02203971042700082</v>
+        <v>0.02735011434650644</v>
       </c>
       <c r="DO22" t="n">
-        <v>-0.03607492076937375</v>
+        <v>0.05287494155217031</v>
       </c>
       <c r="DP22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ22" t="n">
-        <v>0.004550419159549493</v>
+        <v>0.02275070389198072</v>
       </c>
       <c r="DR22" t="n">
-        <v>-0.04351668125551535</v>
+        <v>-0.03405005286906795</v>
       </c>
       <c r="DS22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV22" t="n">
         <v>0</v>
       </c>
       <c r="DW22" t="n">
-        <v>-0.03032986788601249</v>
+        <v>-0.02903851477556511</v>
       </c>
       <c r="DX22" t="n">
-        <v>-0.05057583780196665</v>
+        <v>-0.1118011301444165</v>
       </c>
       <c r="DY22" t="n">
         <v>-0</v>
       </c>
       <c r="DZ22" t="n">
-        <v>0.003529746851967831</v>
+        <v>0.06097451032016491</v>
       </c>
       <c r="EA22" t="n">
-        <v>0.0069005113349596</v>
+        <v>0.1331098073940768</v>
       </c>
       <c r="EB22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED22" t="n">
         <v>0</v>
       </c>
       <c r="EE22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF22" t="n">
-        <v>0.01155256349247485</v>
+        <v>0.1030101266383968</v>
       </c>
       <c r="EG22" t="n">
-        <v>0.0008611121006375251</v>
+        <v>0.06233096132393361</v>
       </c>
       <c r="EH22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI22" t="n">
-        <v>-0.01556731840851587</v>
+        <v>0.05838238938339908</v>
       </c>
       <c r="EJ22" t="n">
-        <v>0.009015495588904373</v>
+        <v>-0.02919369664372179</v>
       </c>
       <c r="EK22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM22" t="n">
         <v>-0</v>
@@ -12811,19 +12811,19 @@
         <v>0</v>
       </c>
       <c r="EO22" t="n">
-        <v>-0.01919228112092314</v>
+        <v>-0.002872475642925334</v>
       </c>
       <c r="EP22" t="n">
-        <v>-0.01977345754234574</v>
+        <v>0.01844381708920223</v>
       </c>
       <c r="EQ22" t="n">
         <v>0</v>
       </c>
       <c r="ER22" t="n">
-        <v>-0.008070006879472125</v>
+        <v>0.02462010779981349</v>
       </c>
       <c r="ES22" t="n">
-        <v>0.06380886221405818</v>
+        <v>0.06619607156303933</v>
       </c>
       <c r="ET22" t="n">
         <v>0</v>
@@ -12835,28 +12835,28 @@
         <v>0</v>
       </c>
       <c r="EW22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX22" t="n">
-        <v>-0.02711447342601173</v>
+        <v>-0.04969038445573137</v>
       </c>
       <c r="EY22" t="n">
-        <v>-0.001432188797807618</v>
+        <v>0.09946215263323116</v>
       </c>
       <c r="EZ22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA22" t="n">
-        <v>-0.0006229010530806238</v>
+        <v>0.06670954988720006</v>
       </c>
       <c r="FB22" t="n">
-        <v>0.01974526977927005</v>
+        <v>-0.019839341626591</v>
       </c>
       <c r="FC22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE22" t="n">
         <v>0</v>
@@ -12865,19 +12865,19 @@
         <v>0</v>
       </c>
       <c r="FG22" t="n">
-        <v>0.01437049600392087</v>
+        <v>-0.04184446677378266</v>
       </c>
       <c r="FH22" t="n">
-        <v>-0.02573765694532458</v>
+        <v>-0.01456950865837402</v>
       </c>
       <c r="FI22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ22" t="n">
-        <v>0.03956751937250255</v>
+        <v>0.02874783436056135</v>
       </c>
       <c r="FK22" t="n">
-        <v>0.03466009255141266</v>
+        <v>0.06295275259872708</v>
       </c>
       <c r="FL22" t="n">
         <v>-0</v>
@@ -12886,64 +12886,64 @@
         <v>0</v>
       </c>
       <c r="FN22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO22" t="n">
         <v>0</v>
       </c>
       <c r="FP22" t="n">
-        <v>-0.03011591527912843</v>
+        <v>-0.04194458043383742</v>
       </c>
       <c r="FQ22" t="n">
-        <v>-0.01785319697441791</v>
+        <v>-0.05238824413294728</v>
       </c>
       <c r="FR22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS22" t="n">
-        <v>-0.01333264522849138</v>
+        <v>0.1581086290686877</v>
       </c>
       <c r="FT22" t="n">
-        <v>0.0464765673453581</v>
+        <v>-0.01338447180758266</v>
       </c>
       <c r="FU22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX22" t="n">
         <v>0</v>
       </c>
       <c r="FY22" t="n">
-        <v>0.01729204243612105</v>
+        <v>-0.01233610639159161</v>
       </c>
       <c r="FZ22" t="n">
-        <v>-0.01690401855778479</v>
+        <v>0.1173250230953145</v>
       </c>
       <c r="GA22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB22" t="n">
-        <v>0.08117438505070469</v>
+        <v>0.06904266931464879</v>
       </c>
       <c r="GC22" t="n">
         <v>-0</v>
       </c>
       <c r="GD22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF22" t="n">
         <v>0</v>
       </c>
       <c r="GG22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
